--- a/docs/exports/pathwave_services_and_costs.xlsx
+++ b/docs/exports/pathwave_services_and_costs.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="₩#,##0;(₩#,##0);-"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,49 +33,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <color rgb="000000FF"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <color rgb="00008000"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <i val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <color rgb="00505050"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -137,9 +142,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -156,13 +162,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -570,176 +576,224 @@
           <t>PathWave 운영비 — 연간 합계 (2026·2027)</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>연도</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>연 합계 (₩)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>월 평균 (₩)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <f>'2026년 월별'!N18</f>
         <v/>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <f>B4/5</f>
         <v/>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>8~12월 (5개월) 실 운영 + 1회성(Apple/Play/Mac mini) 포함</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <f>'2027년 월별'!N18</f>
         <v/>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <f>B5/12</f>
         <v/>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>12개월 — Stage 1→2 점진 성장 + Apple 갱신</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>2년 합계</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>SUM(B4:B5)</f>
         <v/>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>주요 가정</t>
         </is>
       </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>· 환율: USD 1 = ₩1,300 (변동 시 가정 갱신)</t>
         </is>
       </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>· MAU 성장: 2026 8~12월 0~1K → 2027 Q4까지 10K+ (보수적 추정)</t>
         </is>
       </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>· 토스페이먼츠 수수료(2.9%+33원)는 결제 발생 시 매출 차감 — 운영비에 미포함</t>
         </is>
       </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>· Mac mini 옵션 80만원 — 2026년 7월(출시 직전), 자본 여유 시</t>
         </is>
       </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>· 자동화 도구(Stage 2~3 — Channeltalk/ChatGPT/Make/Buffer 등)는 별도 — 도입 시 추가</t>
         </is>
       </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>· 모든 외부 서비스 키는 법인카드 발급 후 법인 명의로 가입</t>
         </is>
       </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>· 신청 체크리스트의 신청 상태가 "활성"으로 바뀐 항목만 실제 비용 발생</t>
         </is>
       </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>사용 방법</t>
         </is>
       </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>① "서비스 신청 체크리스트" 시트의 I열(신청 상태)을 대기→신청중→검수중→활성 으로 갱신</t>
         </is>
       </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>② J/K열(신청일·활성일)을 입력해 신청 진행을 추적</t>
         </is>
       </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>③ 우선순위 1(빨강) → 2(노랑) → 3(회색) 순으로 신청 진행 권장</t>
         </is>
       </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>④ "월별 비용 시나리오" / "2026년·2027년 월별" / "연간 합계" 시트로 비용 예측</t>
         </is>
       </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -774,1438 +828,1438 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>제공사</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>필수/선택</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>청구 방식</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>월 추정 (₩)</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>가입 계정</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>신청 상태</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>신청일</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>활성일</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>환경변수 / 통합 키</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>결제</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>토스페이먼츠</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Toss Payments</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>거래 수수료(2.9%+33원)</t>
         </is>
       </c>
-      <c r="G2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="G2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr"/>
-      <c r="K2" s="15" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr"/>
+      <c r="K2" s="16" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>TOSS_SECRET_KEY, PG_PROVIDER</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>심사 1~2주, 최우선 신청</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>스토어</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Apple Developer</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>연 $99 (~₩128,700)</t>
         </is>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="14" t="n">
         <v>10725</v>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr"/>
-      <c r="K3" s="15" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr"/>
+      <c r="K3" s="16" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>이메일 이관 어려움 → admin@ 필수</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>스토어</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Google Play Console</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>일회성 $25 (~₩32,500)</t>
         </is>
       </c>
-      <c r="G4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr"/>
-      <c r="K4" s="15" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr"/>
+      <c r="K4" s="16" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>일회성 등록</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>호스팅</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>도메인 (pathwave.co.kr)</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Cloudflare / 가비아</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>연 1.5~3만원</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr"/>
-      <c r="K5" s="15" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="16" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>한국 법인 정석</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>호스팅</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Cloudflare DNS/Tunnel</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Cloudflare</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>무료</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr"/>
-      <c r="K6" s="15" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr"/>
+      <c r="K6" s="16" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>DNS + dev 서버 외부 접근</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>호스팅</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>백엔드 서버</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>AWS EC2 / Render / Railway</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>월 5~15만원</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr"/>
-      <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="16" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr">
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t>Flask + gunicorn</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>호스팅</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>PostgreSQL DB</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>AWS RDS / Supabase / Neon</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>월 정액(서버 포함 가능)</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr"/>
-      <c r="K8" s="15" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr"/>
+      <c r="K8" s="16" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>DATABASE_URL</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>마스터 + read 인덱스</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>호스팅</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>프론트 정적 호스팅</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Vercel / Netlify / CFP</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>무료 tier</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr"/>
-      <c r="K9" s="15" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="16" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>admin-web + provider-web</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>인증/푸시</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Firebase Auth + FCM</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>무료 tier</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr"/>
-      <c r="K10" s="15" t="inlineStr"/>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="16" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>FIREBASE_CREDENTIALS, PUSH_PROVIDER</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="13" t="inlineStr">
         <is>
           <t>Google/Apple/이메일 인증 + 푸시</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>이메일도메인</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>월 $7~12/계정</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr"/>
-      <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="16" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>admin/dev/support/info/noreply 5 alias</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>소셜로그인</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>카카오 로그인</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Kakao</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>무료</t>
         </is>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>info@</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr"/>
-      <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="16" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>KAKAO_REST_KEY, KAKAO_NATIVE_APP_KEY</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>카카오 검수 필요 (1~2주)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>소셜로그인</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>네이버 로그인</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Naver</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>무료</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>info@</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="15" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="16" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>NAVER_CLIENT_ID, NAVER_CLIENT_SECRET</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
+      <c r="M13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>알림톡/SMS</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>솔라피 알림톡</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Solapi</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>건당 7~9원</t>
         </is>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="14" t="n">
         <v>45000</v>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J14" s="15" t="inlineStr"/>
-      <c r="K14" s="15" t="inlineStr"/>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="16" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t>SOLAPI_API_KEY, SOLAPI_API_SECRET</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="13" t="inlineStr">
         <is>
           <t>템플릿 사전심사 1~2주</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>알림톡/SMS</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>솔라피 SMS 인증</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Solapi</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>건당 8~15원</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>2400</v>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr"/>
-      <c r="K15" s="15" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="16" t="inlineStr"/>
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>위 키 공용</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>회원가입 인증</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>이메일</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>SendGrid</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>무료 100통/일</t>
         </is>
       </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="G16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="15" t="inlineStr"/>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="16" t="inlineStr"/>
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>EMAIL_PROVIDER, SENDGRID_API_KEY</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="M16" s="13" t="inlineStr">
         <is>
           <t>발신: support@/noreply@</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>모니터링</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Sentry</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Sentry</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>무료 5K/월</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr"/>
-      <c r="K17" s="15" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="16" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>SENTRY_DSN</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr">
+      <c r="M17" s="13" t="inlineStr">
         <is>
           <t>백엔드 통합 완료</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>지도</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Google Maps API</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>월 $200 무료 크레딧</t>
         </is>
       </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="15" t="inlineStr"/>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr"/>
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>GOOGLE_MAPS_API_KEY</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>카드 등록 필수</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>본인인증</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>NICE / KCB / PASS</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>본인인증 사업자</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>건당 30~80원</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr"/>
-      <c r="K19" s="15" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="16" t="inlineStr"/>
+      <c r="L19" s="13" t="inlineStr">
         <is>
           <t>계약 후 키 발급</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr">
+      <c r="M19" s="13" t="inlineStr">
         <is>
           <t>미성년자 확인용</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n">
+      <c r="A20" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>번역</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Google Translate / DeepL</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Google / DeepL</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>선택(P8b)</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>$20/1M chars</t>
         </is>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr"/>
-      <c r="K20" s="15" t="inlineStr"/>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="16" t="inlineStr"/>
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>GOOGLE_TRANSLATE_API_KEY / DEEPL_API_KEY</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
+      <c r="M20" s="13" t="inlineStr">
         <is>
           <t>채팅 자동번역 USP</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n">
+      <c r="A21" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>자동화 S2</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Channeltalk</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Channel.io</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>무료~5만원/월</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr"/>
-      <c r="K21" s="15" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr"/>
+      <c r="K21" s="16" t="inlineStr"/>
+      <c r="L21" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>출시 후 도입</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n">
+      <c r="A22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>자동화 S2</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>ChatGPT API</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>$0.15~3/M tokens</t>
         </is>
       </c>
-      <c r="G22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="G22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr"/>
-      <c r="K22" s="15" t="inlineStr"/>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="16" t="inlineStr"/>
+      <c r="L22" s="13" t="inlineStr">
         <is>
           <t>OPENAI_API_KEY</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M22" s="13" t="inlineStr">
         <is>
           <t>응대/리뷰 응답 자동화</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n">
+      <c r="A23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>자동화 S2</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Make.com</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Make</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>무료~$9~30/월</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="G23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>dev@</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr"/>
-      <c r="K23" s="15" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="16" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>노코드 자동화 허브</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n">
+      <c r="A24" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>자동화 S2</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Buffer / Metricool</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Buffer / Metricool</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>$6~15/월</t>
         </is>
       </c>
-      <c r="G24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="G24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>info@</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr"/>
-      <c r="K24" s="15" t="inlineStr"/>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr"/>
+      <c r="K24" s="16" t="inlineStr"/>
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr">
+      <c r="M24" s="13" t="inlineStr">
         <is>
           <t>SNS 자동 게시</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n">
+      <c r="A25" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>자동화 S3</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>HubSpot CRM</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>HubSpot</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>$20~50/월</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="G25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr"/>
-      <c r="K25" s="15" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="J25" s="16" t="inlineStr"/>
+      <c r="K25" s="16" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr">
+      <c r="M25" s="13" t="inlineStr">
         <is>
           <t>데이터 기반 자동화</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n">
+      <c r="A26" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>자동화 S2</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Twilio Voice</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Twilio</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>선택</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>분당 100~500원</t>
         </is>
       </c>
-      <c r="G26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="G26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>admin@</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J26" s="15" t="inlineStr"/>
-      <c r="K26" s="15" t="inlineStr"/>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr"/>
+      <c r="K26" s="16" t="inlineStr"/>
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>TWILIO_*</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>AI 음성 통화 (Stage 2)</t>
         </is>
@@ -2246,238 +2300,249 @@
           <t>월별 비용 시나리오 — MAU 규모별</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>MAU 1K (출시초기)</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>MAU 10K (중간규모)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>MAU 100K (대규모)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>서버 + DB</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="14" t="n">
         <v>400000</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="14" t="n">
         <v>3500000</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>스케일업</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>도메인 (월할)</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>연 3만원 ÷ 12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>알림톡</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>45000</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>450000</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>4500000</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>5K→50K→500K 건/월</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>SMS + 본인인증</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>500000</v>
       </c>
-      <c r="E7" s="12" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>이메일 (SendGrid)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>tier 초과 시 유료</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>78000</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>5 alias→5 별도 계정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>모니터링 (Sentry 등)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>300000</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>대규모 유료화</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Apple Developer (월할)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>10725</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>10725</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>10725</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>$99/년</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Firebase / 로그인</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>무료 tier</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>소계 (월 합계)</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <f>SUM(B4:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <f>SUM(C4:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>SUM(D4:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>합계 수식</t>
         </is>
@@ -2522,811 +2587,853 @@
           <t>2026년 월별 운영비 추정</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>※ 출시 = 7월 하순~8월 초. 1~7월은 코드 작업 중심. 8월부터 외부 서비스 활성화. MAU 0~1K 가정</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1월</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>4월</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>5월</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>8월</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>9월</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>10월</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>연 합계</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>서버 + DB</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13" t="n">
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="22">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>도메인 (월할)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13" t="n">
+      <c r="B6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="M6" s="13" t="n">
+      <c r="M6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="22">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>알림톡</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13" t="n">
+      <c r="B7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>40000</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>SMS + 본인인증</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13" t="n">
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="M8" s="13" t="n">
+      <c r="M8" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="22">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>이메일 (SendGrid)</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="21">
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="22">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="n">
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="M10" s="13" t="n">
+      <c r="M10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="22">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>모니터링</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="21">
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="22">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Firebase / 로그인</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="21">
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="22">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Google Maps (무료 크레딧 초과분)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="21">
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="22">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>번역 API (P8b)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="21">
+      <c r="B14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="22">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Apple Developer (연회비)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="13" t="n">
+      <c r="B15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
         <v>128700</v>
       </c>
-      <c r="J15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="21">
+      <c r="J15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="22">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Google Play Console (일회성)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13" t="n">
+      <c r="B16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="n">
         <v>32500</v>
       </c>
-      <c r="J16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="21">
+      <c r="J16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="22">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Mac mini 중고 (선택)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
         <v>800000</v>
       </c>
-      <c r="I17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="21">
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="22">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>월 합계</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>SUM(B5:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C5:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(D5:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>SUM(E5:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>SUM(F5:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>SUM(G5:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <f>SUM(H5:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>SUM(I5:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="20">
         <f>SUM(J5:J17)</f>
         <v/>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="20">
         <f>SUM(K5:K17)</f>
         <v/>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="20">
         <f>SUM(L5:L17)</f>
         <v/>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="20">
         <f>SUM(M5:M17)</f>
         <v/>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="20">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="24">
         <f>B18</f>
         <v/>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>B19+C18</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>C19+D18</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>D19+E18</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>E19+F18</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>F19+G18</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="24">
         <f>G19+H18</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="24">
         <f>H19+I18</f>
         <v/>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="24">
         <f>I19+J18</f>
         <v/>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="24">
         <f>J19+K18</f>
         <v/>
       </c>
-      <c r="L19" s="23">
+      <c r="L19" s="24">
         <f>K19+L18</f>
         <v/>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="24">
         <f>L19+M18</f>
         <v/>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="24">
         <f>N18</f>
         <v/>
       </c>
@@ -3371,811 +3478,853 @@
           <t>2027년 월별 운영비 추정</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>※ 점진 성장 가정 — Q1: MAU 1~2K(Stage 1 후반), Q2~Q3: MAU 3~10K(Stage 2), Q4: MAU 10K+. 자동화 도구는 별도</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1월</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>4월</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>5월</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>8월</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>9월</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>10월</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>연 합계</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>서버 + DB</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="14" t="n">
         <v>250000</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="14" t="n">
         <v>250000</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>250000</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <v>400000</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="14" t="n">
         <v>400000</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>400000</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="22">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>도메인 (월할)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="M6" s="13" t="n">
+      <c r="M6" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="22">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>알림톡</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>60000</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>70000</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>130000</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>160000</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="14" t="n">
         <v>200000</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="14" t="n">
         <v>250000</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="14" t="n">
         <v>300000</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>350000</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>400000</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="14" t="n">
         <v>450000</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>SMS + 본인인증</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>6000</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>7000</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <v>25000</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>40000</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="14" t="n">
         <v>45000</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="M8" s="13" t="n">
+      <c r="M8" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="22">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>이메일 (SendGrid)</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="13" t="n">
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="M9" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N9" s="22">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="M10" s="13" t="n">
+      <c r="M10" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="22">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>모니터링</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13" t="n">
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="L11" s="13" t="n">
+      <c r="L11" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="M11" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N11" s="22">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Firebase / 로그인</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="13" t="n">
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="L12" s="13" t="n">
+      <c r="L12" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="M12" s="13" t="n">
+      <c r="M12" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="N12" s="21">
+      <c r="N12" s="22">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Google Maps (무료 크레딧 초과분)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="13" t="n">
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="L13" s="13" t="n">
+      <c r="L13" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="N13" s="21">
+      <c r="N13" s="22">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>번역 API (P8b)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="n">
+      <c r="B14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="14" t="n">
         <v>40000</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="14" t="n">
         <v>60000</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>80000</v>
       </c>
-      <c r="K14" s="13" t="n">
+      <c r="K14" s="14" t="n">
         <v>100000</v>
       </c>
-      <c r="L14" s="13" t="n">
+      <c r="L14" s="14" t="n">
         <v>120000</v>
       </c>
-      <c r="M14" s="13" t="n">
+      <c r="M14" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="N14" s="21">
+      <c r="N14" s="22">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Apple Developer (연회비 갱신)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="13" t="n">
+      <c r="B15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
         <v>128700</v>
       </c>
-      <c r="J15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="21">
+      <c r="J15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="22">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Google Play Console (일회성)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="21">
+      <c r="B16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="22">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Mac mini 중고 (선택)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="21">
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="22">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>월 합계</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>SUM(B5:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C5:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(D5:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>SUM(E5:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>SUM(F5:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>SUM(G5:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <f>SUM(H5:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>SUM(I5:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="20">
         <f>SUM(J5:J17)</f>
         <v/>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="20">
         <f>SUM(K5:K17)</f>
         <v/>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="20">
         <f>SUM(L5:L17)</f>
         <v/>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="20">
         <f>SUM(M5:M17)</f>
         <v/>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="20">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="24">
         <f>B18</f>
         <v/>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>B19+C18</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>C19+D18</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>D19+E18</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>E19+F18</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>F19+G18</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="24">
         <f>G19+H18</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="24">
         <f>H19+I18</f>
         <v/>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="24">
         <f>I19+J18</f>
         <v/>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="24">
         <f>J19+K18</f>
         <v/>
       </c>
-      <c r="L19" s="23">
+      <c r="L19" s="24">
         <f>K19+L18</f>
         <v/>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="24">
         <f>L19+M18</f>
         <v/>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="24">
         <f>N18</f>
         <v/>
       </c>

--- a/docs/exports/pathwave_services_and_costs.xlsx
+++ b/docs/exports/pathwave_services_and_costs.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간 합계" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="서비스 신청 체크리스트" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 비용 시나리오" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026년 월별" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027년 월별" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="초기 세팅비 (1회성)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 운영비 시나리오" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026년 월별" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027년 월별" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,11 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="₩#,##0;(₩#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,19 +59,16 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <color rgb="00008000"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <i val="1"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -83,7 +80,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -107,12 +104,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFCC"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,36 +144,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,20 +182,26 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -561,13 +569,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -615,7 +623,7 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>'2026년 월별'!N18</f>
+        <f>'2026년 월별'!N22</f>
         <v/>
       </c>
       <c r="C4" s="6">
@@ -624,7 +632,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>8~12월 (5개월) 실 운영 + 1회성(Apple/Play/Mac mini) 포함</t>
+          <t>6월 외부 신청 시작, 8~12월 (5개월) 실 운영 + 7월 1회성 포함</t>
         </is>
       </c>
     </row>
@@ -635,7 +643,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'2027년 월별'!N18</f>
+        <f>'2027년 월별'!N22</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -644,7 +652,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>12개월 — Stage 1→2 점진 성장 + Apple 갱신</t>
+          <t>12개월 — Q1~Q4 점진 성장 + 도메인·Apple 연 갱신</t>
         </is>
       </c>
     </row>
@@ -668,7 +676,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>주요 가정</t>
+          <t>주요 가정 / 변경점 (2026-05-23 갱신)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -678,7 +686,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>· 환율: USD 1 = ₩1,300 (변동 시 가정 갱신)</t>
+          <t>① 외부 서비스 신청 시작 = 2026-06-02 주 (법인카드 수취 후). 그 전 = 코드 작업만, 비용 거의 0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -688,7 +696,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>· MAU 성장: 2026 8~12월 0~1K → 2027 Q4까지 10K+ (보수적 추정)</t>
+          <t>② 이메일·도메인: 패스웨이브(서비스 — pathwave.co.kr) + 트리거소프트(법인 — triggersoft.kr) 분리</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -698,7 +706,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>· 토스페이먼츠 수수료(2.9%+33원)는 결제 발생 시 매출 차감 — 운영비에 미포함</t>
+          <t xml:space="preserve">   Google Workspace 2계정 ($7×2 = ₩18,200/월), 패스웨이브는 4 alias로 5메일 운영</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -708,7 +716,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>· Mac mini 옵션 80만원 — 2026년 7월(출시 직전), 자본 여유 시</t>
+          <t>③ 알림톡 비용 현실화 — 매장당 월 2건 쿠폰/이벤트 × 평균 50명 = 100건/매장/월 × 9원</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -718,7 +726,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>· 자동화 도구(Stage 2~3 — Channeltalk/ChatGPT/Make/Buffer 등)는 별도 — 도입 시 추가</t>
+          <t xml:space="preserve">   MAU 1K(매장 10) ₩9,000 / MAU 10K(매장 100) ₩90,000 / MAU 100K(매장 500) ₩450,000</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -728,7 +736,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>· 모든 외부 서비스 키는 법인카드 발급 후 법인 명의로 가입</t>
+          <t>④ 초기 세팅비(Apple·Play·도메인·Mac mini·NICE)는 별도 시트로 분리, 월별 시트에서는 발생 월에 일시불 표시</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -738,7 +746,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>· 신청 체크리스트의 신청 상태가 "활성"으로 바뀐 항목만 실제 비용 발생</t>
+          <t>⑤ 환율: USD 1 = ₩1,300 (변동 시 가정 갱신)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -746,9 +754,9 @@
       <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>사용 방법</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>⑥ 토스페이먼츠 수수료(2.9% + 33원)는 결제 발생 시 매출 차감 — 운영비 미포함</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -758,7 +766,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>① "서비스 신청 체크리스트" 시트의 I열(신청 상태)을 대기→신청중→검수중→활성 으로 갱신</t>
+          <t>⑦ Mac mini 옵션 80만원·NICE 보증금 10만원 — 자본 여유 시 도입 (필수 아님)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -768,7 +776,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>② J/K열(신청일·활성일)을 입력해 신청 진행을 추적</t>
+          <t>⑧ 모든 외부 서비스 키는 법인카드 발급 후 법인 명의 가입 (개인 → 법인 이관 어려움)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -778,7 +786,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>③ 우선순위 1(빨강) → 2(노랑) → 3(회색) 순으로 신청 진행 권장</t>
+          <t>⑨ 자동화 도구(Stage 2~3 — Channeltalk·ChatGPT·Make 등) = 출시 후 매출 발생 시 단계적 도입</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -786,14 +794,64 @@
       <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>④ "월별 비용 시나리오" / "2026년·2027년 월별" / "연간 합계" 시트로 비용 예측</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>사용 방법</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>① "서비스 신청 체크리스트": I열 신청 상태(대기→신청중→검수중→활성) 갱신</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>② "초기 세팅비": 출시 전 1회성 비용 — 필수만 vs 옵션 포함 두 합계</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>③ "월별 운영비 시나리오": MAU 1K/10K/100K 별 매월 발생 비용</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>④ "2026/2027년 월별": 반복 + 1회성 통합 cash flow view, 누계 자동 계산</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>⑤ "연간 합계": 연·월 평균 + 주요 가정</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -809,22 +867,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -855,12 +912,12 @@
       </c>
       <c r="F1" s="11" t="inlineStr">
         <is>
-          <t>청구 방식</t>
+          <t>월 추정 (₩)</t>
         </is>
       </c>
       <c r="G1" s="11" t="inlineStr">
         <is>
-          <t>월 추정 (₩)</t>
+          <t>초기 세팅비 (₩)</t>
         </is>
       </c>
       <c r="H1" s="11" t="inlineStr">
@@ -875,22 +932,17 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>신청일</t>
+          <t>신청 예정</t>
         </is>
       </c>
       <c r="K1" s="11" t="inlineStr">
         <is>
-          <t>활성일</t>
+          <t>활성 예정</t>
         </is>
       </c>
       <c r="L1" s="11" t="inlineStr">
         <is>
-          <t>환경변수 / 통합 키</t>
-        </is>
-      </c>
-      <c r="M1" s="11" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>환경변수 / 비고</t>
         </is>
       </c>
     </row>
@@ -918,17 +970,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>거래 수수료(2.9%+33원)</t>
-        </is>
+      <c r="F2" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
@@ -936,16 +986,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr"/>
-      <c r="K2" s="16" t="inlineStr"/>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
-          <t>TOSS_SECRET_KEY, PG_PROVIDER</t>
-        </is>
-      </c>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>심사 1~2주, 최우선 신청</t>
+          <t>TOSS_SECRET_KEY · 심사 1~2주 (가장 김)</t>
         </is>
       </c>
     </row>
@@ -973,17 +1026,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>연 $99 (~₩128,700)</t>
-        </is>
+      <c r="F3" s="14" t="n">
+        <v>10725</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>10725</v>
+        <v>128700</v>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I3" s="15" t="inlineStr">
@@ -991,16 +1042,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr"/>
-      <c r="K3" s="16" t="inlineStr"/>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M3" s="13" t="inlineStr">
-        <is>
-          <t>이메일 이관 어려움 → admin@ 필수</t>
+          <t>$99/년 일시불, 이메일 이관 어려움</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1082,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>일회성 $25 (~₩32,500)</t>
-        </is>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>32500</v>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
@@ -1046,16 +1098,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr"/>
-      <c r="K4" s="16" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
       <c r="L4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>일회성 등록</t>
+          <t>$25 일회성</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1120,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>도메인</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>도메인 (pathwave.co.kr)</t>
+          <t>pathwave.co.kr (서비스)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -1083,17 +1138,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>연 1.5~3만원</t>
-        </is>
+      <c r="F5" s="14" t="n">
+        <v>2500</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2500</v>
+        <v>30000</v>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1101,16 +1154,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="16" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>한국 법인 정석</t>
+          <t>연 3만원 ÷ 12</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1176,17 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>도메인</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Cloudflare DNS/Tunnel</t>
+          <t>triggersoft.kr (법인)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Cloudflare / 가비아</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1138,17 +1194,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>무료</t>
-        </is>
+      <c r="F6" s="14" t="n">
+        <v>2500</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@triggersoft</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1156,16 +1210,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>DNS + dev 서버 외부 접근</t>
+          <t>법인 사업·세무·회계용</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1237,12 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>백엔드 서버</t>
+          <t>Cloudflare DNS/Tunnel</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>AWS EC2 / Render / Railway</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -1193,17 +1250,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>월 5~15만원</t>
-        </is>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1211,16 +1266,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>Flask + gunicorn</t>
+          <t>무료 — DNS + dev 서버 외부 접근</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1293,12 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>PostgreSQL DB</t>
+          <t>백엔드 서버</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>AWS RDS / Supabase / Neon</t>
+          <t>AWS EC2 / Render / Railway</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -1248,17 +1306,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>월 정액(서버 포함 가능)</t>
-        </is>
+      <c r="F8" s="14" t="n">
+        <v>50000</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -1266,16 +1322,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>DATABASE_URL</t>
-        </is>
-      </c>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>마스터 + read 인덱스</t>
+          <t>Flask + gunicorn</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1349,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>프론트 정적 호스팅</t>
+          <t>PostgreSQL DB</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Vercel / Netlify / CFP</t>
+          <t>AWS RDS / Supabase / Neon</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -1303,17 +1362,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>무료 tier</t>
-        </is>
+      <c r="F9" s="14" t="n">
+        <v>30000</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1321,16 +1378,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="inlineStr">
-        <is>
-          <t>admin-web + provider-web</t>
+          <t>DATABASE_URL</t>
         </is>
       </c>
     </row>
@@ -1340,17 +1400,17 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>인증/푸시</t>
+          <t>호스팅</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Firebase Auth + FCM</t>
+          <t>프론트 정적 호스팅</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Vercel / Netlify / CFP</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -1358,34 +1418,35 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>admin@pathwave</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>무료 tier</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>dev@</t>
-        </is>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>FIREBASE_CREDENTIALS, PUSH_PROVIDER</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="inlineStr">
-        <is>
-          <t>Google/Apple/이메일 인증 + 푸시</t>
         </is>
       </c>
     </row>
@@ -1395,160 +1456,167 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
+          <t>인증/푸시</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Firebase Auth + FCM</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>dev@pathwave</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>FIREBASE_CREDENTIALS · 무료 tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
           <t>이메일도메인</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Google Workspace</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Google Workspace (Pathwave)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>월 $7~12/계정</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>15600</v>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>admin@</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="F12" s="14" t="n">
+        <v>9100</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>admin@pathwave</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="inlineStr">
-        <is>
-          <t>admin/dev/support/info/noreply 5 alias</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>소셜로그인</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>카카오 로그인</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Kakao</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>$7 × 1계정 + 4 alias (admin/dev/support/noreply/info)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>이메일도메인</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Google Workspace (Triggersoft)</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>무료</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>info@</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="F13" s="14" t="n">
+        <v>9100</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>admin@triggersoft</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>KAKAO_REST_KEY, KAKAO_NATIVE_APP_KEY</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="inlineStr">
-        <is>
-          <t>카카오 검수 필요 (1~2주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>소셜로그인</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>네이버 로그인</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Naver</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>무료</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>info@</t>
-        </is>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>NAVER_CLIENT_ID, NAVER_CLIENT_SECRET</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr"/>
+          <t>$7 × 1계정 (법인 운영)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
@@ -1556,17 +1624,17 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>알림톡/SMS</t>
+          <t>소셜로그인</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>솔라피 알림톡</t>
+          <t>카카오 로그인</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Solapi</t>
+          <t>Kakao</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1574,17 +1642,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>건당 7~9원</t>
-        </is>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>info@pathwave</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -1592,16 +1658,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>SOLAPI_API_KEY, SOLAPI_API_SECRET</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr">
-        <is>
-          <t>템플릿 사전심사 1~2주</t>
+          <t>KAKAO_REST_KEY · 검수 1~2주</t>
         </is>
       </c>
     </row>
@@ -1611,17 +1680,17 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>알림톡/SMS</t>
+          <t>소셜로그인</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>솔라피 SMS 인증</t>
+          <t>네이버 로그인</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Solapi</t>
+          <t>Naver</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1629,17 +1698,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>건당 8~15원</t>
-        </is>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>info@pathwave</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
@@ -1647,16 +1714,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>위 키 공용</t>
-        </is>
-      </c>
-      <c r="M15" s="13" t="inlineStr">
-        <is>
-          <t>회원가입 인증</t>
+          <t>NAVER_CLIENT_ID</t>
         </is>
       </c>
     </row>
@@ -1666,17 +1736,17 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>이메일</t>
+          <t>알림톡/SMS</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>SendGrid</t>
+          <t>솔라피 알림톡</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Solapi</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1684,17 +1754,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>무료 100통/일</t>
-        </is>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -1702,16 +1770,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>EMAIL_PROVIDER, SENDGRID_API_KEY</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="inlineStr">
-        <is>
-          <t>발신: support@/noreply@</t>
+          <t>템플릿 사전심사 1~2주, 건당 9원 (사용량 기반)</t>
         </is>
       </c>
     </row>
@@ -1721,17 +1792,17 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>모니터링</t>
+          <t>알림톡/SMS</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>솔라피 SMS 인증</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Solapi</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1739,17 +1810,15 @@
           <t>필수</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>무료 5K/월</t>
-        </is>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
@@ -1757,16 +1826,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>SENTRY_DSN</t>
-        </is>
-      </c>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>백엔드 통합 완료</t>
+          <t>건당 8~15원</t>
         </is>
       </c>
     </row>
@@ -1776,162 +1848,165 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>SendGrid</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>dev@pathwave</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>무료 100통/일 · 발신: support@</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>모니터링</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Sentry</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>dev@pathwave</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>무료 5K events/월</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
           <t>지도</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Google Maps API</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>dev@pathwave</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>월 $200 무료 크레딧</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>dev@</t>
-        </is>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>GOOGLE_MAPS_API_KEY</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr">
-        <is>
-          <t>카드 등록 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>본인인증</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>NICE / KCB / PASS</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>본인인증 사업자</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>건당 30~80원</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>admin@</t>
-        </is>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>계약 후 키 발급</t>
-        </is>
-      </c>
-      <c r="M19" s="13" t="inlineStr">
-        <is>
-          <t>미성년자 확인용</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>번역</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Google Translate / DeepL</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Google / DeepL</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>선택(P8b)</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>$20/1M chars</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>dev@</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>GOOGLE_TRANSLATE_API_KEY / DEEPL_API_KEY</t>
-        </is>
-      </c>
-      <c r="M20" s="13" t="inlineStr">
-        <is>
-          <t>채팅 자동번역 USP</t>
         </is>
       </c>
     </row>
@@ -1941,17 +2016,17 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>자동화 S2</t>
+          <t>본인인증</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Channeltalk</t>
+          <t>NICE / KCB / PASS</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Channel.io</t>
+          <t>본인인증 사업자</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1959,17 +2034,15 @@
           <t>선택</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>무료~5만원/월</t>
-        </is>
+      <c r="F21" s="14" t="n">
+        <v>2500</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I21" s="15" t="inlineStr">
@@ -1977,16 +2050,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-말</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-중</t>
+        </is>
+      </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>출시 후 도입</t>
+          <t>계약 보증금 + 건당 30~80원</t>
         </is>
       </c>
     </row>
@@ -1996,17 +2072,17 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>자동화 S2</t>
+          <t>번역</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>ChatGPT API</t>
+          <t>Google Translate / DeepL</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google / DeepL</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -2014,17 +2090,15 @@
           <t>선택</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>$0.15~3/M tokens</t>
-        </is>
+      <c r="F22" s="14" t="n">
+        <v>30000</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -2032,16 +2106,19 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr"/>
-      <c r="K22" s="16" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-초</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-중</t>
+        </is>
+      </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
-          <t>OPENAI_API_KEY</t>
-        </is>
-      </c>
-      <c r="M22" s="13" t="inlineStr">
-        <is>
-          <t>응대/리뷰 응답 자동화</t>
+          <t>P8b 채팅 자동번역 USP</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2133,12 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Make.com</t>
+          <t>Channeltalk</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Make</t>
+          <t>Channel.io</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -2069,17 +2146,15 @@
           <t>선택</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>무료~$9~30/월</t>
-        </is>
+      <c r="F23" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>dev@</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -2087,16 +2162,15 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>출시 후</t>
+        </is>
+      </c>
       <c r="K23" s="16" t="inlineStr"/>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="13" t="inlineStr">
-        <is>
-          <t>노코드 자동화 허브</t>
+          <t>무료~5만원/월</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2185,12 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>Buffer / Metricool</t>
+          <t>ChatGPT API</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Buffer / Metricool</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -2124,17 +2198,15 @@
           <t>선택</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>$6~15/월</t>
-        </is>
+      <c r="F24" s="14" t="n">
+        <v>30000</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>info@</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
@@ -2142,16 +2214,15 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr"/>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>출시 후</t>
+        </is>
+      </c>
       <c r="K24" s="16" t="inlineStr"/>
       <c r="L24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>SNS 자동 게시</t>
+          <t>OPENAI_API_KEY · 응대 자동화</t>
         </is>
       </c>
     </row>
@@ -2161,17 +2232,17 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>자동화 S3</t>
+          <t>자동화 S2</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>HubSpot CRM</t>
+          <t>Make.com</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>Make</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -2179,17 +2250,15 @@
           <t>선택</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>$20~50/월</t>
-        </is>
+      <c r="F25" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
@@ -2197,16 +2266,15 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>출시 후</t>
+        </is>
+      </c>
       <c r="K25" s="16" t="inlineStr"/>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>데이터 기반 자동화</t>
+          <t>무료~$9~30/월</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2289,12 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Twilio Voice</t>
+          <t>Buffer / Metricool</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Buffer / Metricool</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -2234,17 +2302,15 @@
           <t>선택</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>분당 100~500원</t>
-        </is>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>admin@</t>
+          <t>info@pathwave</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
@@ -2252,25 +2318,152 @@
           <t>대기</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>출시 후</t>
+        </is>
+      </c>
       <c r="K26" s="16" t="inlineStr"/>
       <c r="L26" s="13" t="inlineStr">
         <is>
-          <t>TWILIO_*</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr">
-        <is>
-          <t>AI 음성 통화 (Stage 2)</t>
-        </is>
-      </c>
+          <t>SNS 자동 게시</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>자동화 S3</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>HubSpot CRM</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>admin@pathwave</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>+3개월</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>$20~50/월</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>자동화 S2</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Twilio Voice</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>admin@pathwave</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>+3개월</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>AI 음성 통화</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr"/>
+      <c r="B29" s="13" t="inlineStr"/>
+      <c r="C29" s="13" t="inlineStr"/>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr"/>
+      <c r="F29" s="20">
+        <f>SUM(F2:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="20">
+        <f>SUM(G2:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="13" t="inlineStr"/>
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"대기,신청중,검수중,활성,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2284,33 +2477,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>월별 비용 시나리오 — MAU 규모별</t>
+          <t>초기 세팅비 — 출시 전 1회성 / 연 1회 비용</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -2320,20 +2510,15 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>MAU 1K (출시초기)</t>
+          <t>금액 (₩)</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>MAU 10K (중간규모)</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>MAU 100K (대규모)</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2342,215 +2527,320 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>서버 + DB</t>
+          <t>Apple Developer Program 첫 회비</t>
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>스케일업</t>
+        <v>128700</v>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>$99/년 (USD 1=₩1,300)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>도메인 (월할)</t>
+          <t>Google Play Console 등록비</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>연 3만원 ÷ 12</t>
+        <v>32500</v>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>$25 일회성</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>알림톡</t>
+          <t>도메인 첫 등록 — pathwave.co.kr</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>5K→50K→500K 건/월</t>
+        <v>30000</v>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>서비스 도메인</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>SMS + 본인인증</t>
+          <t>도메인 첫 등록 — triggersoft.kr</t>
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E7" s="13" t="inlineStr"/>
+        <v>30000</v>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>법인 운영 도메인</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>Mac mini M1 16GB/256GB 중고 (선택)</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>tier 초과 시 유료</t>
+        <v>800000</v>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>자본 여유 시 — 24/7 운영 베이스</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>Mac mini 주변 (외장 SSD, 케이블 등)</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>15600</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>15600</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>78000</v>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>5 alias→5 별도 계정</t>
+        <v>80000</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Mac mini 옵션 시</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>모니터링 (Sentry 등)</t>
+          <t>NICE 본인인증 계약 보증금 (선택)</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>대규모 유료화</t>
+        <v>100000</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>미성년자 확인 도입 시</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Apple Developer (월할)</t>
+          <t>카카오 로그인 검수</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>10725</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>10725</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>10725</v>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>$99/년</t>
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>무료, 1~2주 소요</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Firebase / 로그인</t>
+          <t>네이버 로그인 가입</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>무료 tier</t>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>무료</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>소계 (월 합계)</t>
-        </is>
-      </c>
-      <c r="B13" s="20">
-        <f>SUM(B4:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="20">
-        <f>SUM(C4:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="20">
-        <f>SUM(D4:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>합계 수식</t>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>솔라피 알림톡 템플릿 등록·심사</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>무료, 1~2주 소요</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>토스페이먼츠 가맹점 가입</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>무료, 심사 1~2주</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>사업자등록 (홈택스)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>무료 — 법인등기 후 즉시</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>통신판매업 신고</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>무료 — 구청</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>위치기반서비스사업 신고</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>일회성</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>무료 — 방통위, 수 주 소요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>소계 — 필수만 (Mac mini·본인인증 제외)</t>
+        </is>
+      </c>
+      <c r="B18" s="20">
+        <f>SUM(B4:B7)+SUM(B11:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="13" t="inlineStr"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Mac mini·NICE 옵션 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>소계 — 옵션 포함 (Mac mini + NICE)</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>SUM(B4:B17)</f>
+        <v/>
+      </c>
+      <c r="C19" s="13" t="inlineStr"/>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>전체 포함</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2562,10 +2852,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>월별 운영비 시나리오 — MAU 규모별 (사용량 기반 반복 비용만)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>MAU 1K (매장 10)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>MAU 10K (매장 100)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>MAU 100K (매장 500)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>서버 + DB</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Render→Railway→AWS RDS 점진</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>도메인 (2개 × 월할)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>pathwave + triggersoft 연 3만원 × 2 ÷ 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>알림톡 (매장당 100건/월)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>매장 × 100건 × 9원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>SMS 인증 + 본인인증</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>회원가입·결제 시</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>이메일 (SendGrid)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>무료 100통/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Google Workspace (2계정 × $7)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>18200</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>18200</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>18200</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>pathwave + triggersoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>모니터링 (Sentry)</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>무료 5K → 대규모만 유료</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Firebase / 로그인</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>무료 tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Google Maps (초과분)</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>월 $200 크레딧</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>월 운영비 합계</t>
+        </is>
+      </c>
+      <c r="B13" s="20">
+        <f>SUM(B4:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="20">
+        <f>SUM(C4:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>SUM(D4:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -2584,7 +3152,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026년 월별 운영비 추정</t>
+          <t>2026년 월별 운영비 (반복 + 일회성)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2602,9 +3170,9 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>※ 출시 = 7월 하순~8월 초. 1~7월은 코드 작업 중심. 8월부터 외부 서비스 활성화. MAU 0~1K 가정</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>※ 출시 = 2026-07 하순~08-초. 1~5월 코드 작업. 6/2주 법인카드 수취 → 외부 서비스 일괄 신청. 6월 도메인·Workspace 셋업, 7월 Apple/Google Play 결제 + Mac mini·NICE(옵션), 8월 출시 후 MAU 0~1K</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2710,56 +3278,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>서버 + DB</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N5" s="22">
-        <f>SUM(B5:M5)</f>
-        <v/>
-      </c>
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>【 반복 비용 (월 정액·사용량) 】</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="inlineStr"/>
+      <c r="N5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>도메인 (월할)</t>
+          <t>서버 + DB</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
@@ -2781,24 +3322,24 @@
         <v>0</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="M6" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N6" s="22">
+        <v>80000</v>
+      </c>
+      <c r="N6" s="24">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2806,7 +3347,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>알림톡</t>
+          <t>도메인 (월할)</t>
         </is>
       </c>
       <c r="B7" s="14" t="n">
@@ -2825,27 +3366,27 @@
         <v>0</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N7" s="22">
+        <v>5000</v>
+      </c>
+      <c r="N7" s="24">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -2853,7 +3394,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>SMS + 본인인증</t>
+          <t>알림톡 (사용량)</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
@@ -2878,21 +3419,21 @@
         <v>0</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="M8" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N8" s="22">
+        <v>9000</v>
+      </c>
+      <c r="N8" s="24">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -2900,7 +3441,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>SMS + 본인인증</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
@@ -2925,21 +3466,21 @@
         <v>0</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="22">
+        <v>5000</v>
+      </c>
+      <c r="N9" s="24">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -2947,7 +3488,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>이메일 (SendGrid)</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
@@ -2969,24 +3510,24 @@
         <v>0</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="M10" s="14" t="n">
-        <v>15600</v>
-      </c>
-      <c r="N10" s="22">
+        <v>0</v>
+      </c>
+      <c r="N10" s="24">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -2994,7 +3535,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>모니터링</t>
+          <t>Google Workspace (2계정)</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
@@ -3013,27 +3554,27 @@
         <v>0</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="22">
+        <v>18200</v>
+      </c>
+      <c r="N11" s="24">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -3041,7 +3582,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Firebase / 로그인</t>
+          <t>모니터링</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
@@ -3080,7 +3621,7 @@
       <c r="M12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="22">
+      <c r="N12" s="24">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -3088,7 +3629,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Google Maps (무료 크레딧 초과분)</t>
+          <t>Firebase / 로그인</t>
         </is>
       </c>
       <c r="B13" s="14" t="n">
@@ -3127,7 +3668,7 @@
       <c r="M13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="22">
+      <c r="N13" s="24">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -3135,7 +3676,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>번역 API (P8b)</t>
+          <t>Google Maps (초과분)</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
@@ -3174,7 +3715,7 @@
       <c r="M14" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="24">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -3182,7 +3723,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Apple Developer (연회비)</t>
+          <t>번역 API (P8b)</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
@@ -3207,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>128700</v>
+        <v>0</v>
       </c>
       <c r="J15" s="14" t="n">
         <v>0</v>
@@ -3221,62 +3762,35 @@
       <c r="M15" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="24">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Google Play Console (일회성)</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>32500</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="22">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>【 초기 세팅비 / 1회성 】</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr"/>
+      <c r="C16" s="13" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="13" t="inlineStr"/>
+      <c r="M16" s="13" t="inlineStr"/>
+      <c r="N16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Mac mini 중고 (선택)</t>
+          <t>도메인 첫 등록 (pathwave + triggersoft)</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
@@ -3295,146 +3809,334 @@
         <v>0</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="H17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="24">
+        <f>SUM(B17:M17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Apple Developer ($99/년)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>128700</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="24">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Google Play Console ($25)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="24">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Mac mini 중고 (선택, 자본 여유 시)</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
         <v>800000</v>
       </c>
-      <c r="I17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="22">
-        <f>SUM(B17:M17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="I20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="24">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>NICE 본인인증 보증금 (선택)</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="24">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>월 합계</t>
         </is>
       </c>
-      <c r="B18" s="20">
-        <f>SUM(B5:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="20">
-        <f>SUM(C5:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="20">
-        <f>SUM(D5:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="20">
-        <f>SUM(E5:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="20">
-        <f>SUM(F5:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="20">
-        <f>SUM(G5:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="20">
-        <f>SUM(H5:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="20">
-        <f>SUM(I5:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="20">
-        <f>SUM(J5:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="20">
-        <f>SUM(K5:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="20">
-        <f>SUM(L5:L17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="20">
-        <f>SUM(M5:M17)</f>
-        <v/>
-      </c>
-      <c r="N18" s="20">
-        <f>SUM(B18:M18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="B22" s="20">
+        <f>SUM(B6:B15)+SUM(B17:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>SUM(C6:C15)+SUM(C17:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>SUM(D6:D15)+SUM(D17:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>SUM(E6:E15)+SUM(E17:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="20">
+        <f>SUM(F6:F15)+SUM(F17:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
+        <f>SUM(G6:G15)+SUM(G17:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="20">
+        <f>SUM(H6:H15)+SUM(H17:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="20">
+        <f>SUM(I6:I15)+SUM(I17:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="20">
+        <f>SUM(J6:J15)+SUM(J17:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="20">
+        <f>SUM(K6:K15)+SUM(K17:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="20">
+        <f>SUM(L6:L15)+SUM(L17:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="20">
+        <f>SUM(M6:M15)+SUM(M17:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="20">
+        <f>SUM(B22:M22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B19" s="24">
-        <f>B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="24">
-        <f>B19+C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>C19+D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>D19+E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>E19+F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
-        <f>F19+G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="24">
-        <f>G19+H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
-        <f>H19+I18</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>I19+J18</f>
-        <v/>
-      </c>
-      <c r="K19" s="24">
-        <f>J19+K18</f>
-        <v/>
-      </c>
-      <c r="L19" s="24">
-        <f>K19+L18</f>
-        <v/>
-      </c>
-      <c r="M19" s="24">
-        <f>L19+M18</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>N18</f>
+      <c r="B23" s="26">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="26">
+        <f>B23+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="26">
+        <f>C23+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="26">
+        <f>D23+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="26">
+        <f>E23+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="26">
+        <f>F23+G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="26">
+        <f>G23+H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="26">
+        <f>H23+I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="26">
+        <f>I23+J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="26">
+        <f>J23+K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="26">
+        <f>K23+L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="26">
+        <f>L23+M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="26">
+        <f>N22</f>
         <v/>
       </c>
     </row>
@@ -3447,16 +4149,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -3475,7 +4177,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2027년 월별 운영비 추정</t>
+          <t>2027년 월별 운영비 (반복 + 일회성)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3493,9 +4195,9 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>※ 점진 성장 가정 — Q1: MAU 1~2K(Stage 1 후반), Q2~Q3: MAU 3~10K(Stage 2), Q4: MAU 10K+. 자동화 도구는 별도</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>※ 점진 성장 가정 — Q1: 매장 20~30(MAU 1~2K), Q2: 매장 50(MAU 3~5K), Q3: 매장 100(MAU 5~10K), Q4: 매장 200(MAU 10K+). 알림톡 = 매장당 100건/월 × 9원 (현실적 가정)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3601,95 +4303,68 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>서버 + DB</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>250000</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L5" s="14" t="n">
-        <v>400000</v>
-      </c>
-      <c r="M5" s="14" t="n">
-        <v>400000</v>
-      </c>
-      <c r="N5" s="22">
-        <f>SUM(B5:M5)</f>
-        <v/>
-      </c>
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>【 반복 비용 (월 정액·사용량) 】</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="inlineStr"/>
+      <c r="N5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>도메인 (월할)</t>
+          <t>서버 + DB</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>2500</v>
+        <v>100000</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2500</v>
+        <v>100000</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2500</v>
+        <v>100000</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>2500</v>
+        <v>150000</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>2500</v>
+        <v>150000</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>2500</v>
+        <v>150000</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>2500</v>
+        <v>200000</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>2500</v>
+        <v>200000</v>
       </c>
       <c r="M6" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N6" s="22">
+        <v>200000</v>
+      </c>
+      <c r="N6" s="24">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -3697,46 +4372,46 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>알림톡</t>
+          <t>도메인 (월할)</t>
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>60000</v>
+        <v>5000</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>70000</v>
+        <v>5000</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>130000</v>
+        <v>5000</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>160000</v>
+        <v>5000</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>200000</v>
+        <v>5000</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>250000</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>300000</v>
+        <v>5000</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>350000</v>
+        <v>5000</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>400000</v>
+        <v>5000</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>450000</v>
-      </c>
-      <c r="N7" s="22">
+        <v>5000</v>
+      </c>
+      <c r="N7" s="24">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -3744,46 +4419,46 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>SMS + 본인인증</t>
+          <t>알림톡 (사용량)</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>6000</v>
+        <v>22500</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>10000</v>
+        <v>36000</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>15000</v>
+        <v>40500</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>25000</v>
+        <v>63000</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>30000</v>
+        <v>72000</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>45000</v>
+        <v>135000</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>50000</v>
+        <v>153000</v>
       </c>
       <c r="M8" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N8" s="22">
+        <v>180000</v>
+      </c>
+      <c r="N8" s="24">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -3791,46 +4466,46 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>SMS + 본인인증</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="N9" s="22">
+        <v>45000</v>
+      </c>
+      <c r="N9" s="24">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -3838,46 +4513,46 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>이메일 (SendGrid)</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>15600</v>
+        <v>3000</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>15600</v>
+        <v>3000</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>15600</v>
+        <v>5000</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>15600</v>
+        <v>5000</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>15600</v>
+        <v>8000</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>15600</v>
+        <v>10000</v>
       </c>
       <c r="M10" s="14" t="n">
-        <v>15600</v>
-      </c>
-      <c r="N10" s="22">
+        <v>12000</v>
+      </c>
+      <c r="N10" s="24">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -3885,46 +4560,46 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>모니터링</t>
+          <t>Google Workspace (2계정)</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>30000</v>
+        <v>18200</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>30000</v>
+        <v>18200</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>30000</v>
+        <v>18200</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>50000</v>
+        <v>18200</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>50000</v>
+        <v>18200</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N11" s="22">
+        <v>18200</v>
+      </c>
+      <c r="N11" s="24">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -3932,7 +4607,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Firebase / 로그인</t>
+          <t>모니터링</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
@@ -3960,18 +4635,18 @@
         <v>0</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>20000</v>
-      </c>
-      <c r="N12" s="22">
+        <v>30000</v>
+      </c>
+      <c r="N12" s="24">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -3979,7 +4654,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Google Maps (무료 크레딧 초과분)</t>
+          <t>Firebase / 로그인</t>
         </is>
       </c>
       <c r="B13" s="14" t="n">
@@ -4010,15 +4685,15 @@
         <v>0</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>30000</v>
-      </c>
-      <c r="N13" s="22">
+        <v>20000</v>
+      </c>
+      <c r="N13" s="24">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -4026,7 +4701,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>번역 API (P8b)</t>
+          <t>Google Maps (초과분)</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
@@ -4039,33 +4714,33 @@
         <v>0</v>
       </c>
       <c r="E14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L14" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="M14" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>40000</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>60000</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>80000</v>
-      </c>
-      <c r="K14" s="14" t="n">
-        <v>100000</v>
-      </c>
-      <c r="L14" s="14" t="n">
-        <v>120000</v>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>150000</v>
-      </c>
-      <c r="N14" s="22">
+      <c r="N14" s="24">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -4073,7 +4748,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Apple Developer (연회비 갱신)</t>
+          <t>번역 API (P8b)</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
@@ -4086,88 +4761,61 @@
         <v>0</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>128700</v>
+        <v>30000</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="22">
+        <v>80000</v>
+      </c>
+      <c r="N15" s="24">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Google Play Console (일회성)</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="22">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>【 초기 세팅비 / 1회성 】</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr"/>
+      <c r="C16" s="13" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="13" t="inlineStr"/>
+      <c r="M16" s="13" t="inlineStr"/>
+      <c r="N16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Mac mini 중고 (선택)</t>
+          <t>Apple Developer (연 갱신)</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
@@ -4189,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>0</v>
+        <v>128700</v>
       </c>
       <c r="I17" s="14" t="n">
         <v>0</v>
@@ -4206,126 +4854,314 @@
       <c r="M17" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="22">
+      <c r="N17" s="24">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Google Play Console</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="24">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Mac mini</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="24">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>NICE 본인인증</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="24">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>도메인 (연 갱신)</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="24">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>월 합계</t>
         </is>
       </c>
-      <c r="B18" s="20">
-        <f>SUM(B5:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="20">
-        <f>SUM(C5:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="20">
-        <f>SUM(D5:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="20">
-        <f>SUM(E5:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="20">
-        <f>SUM(F5:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="20">
-        <f>SUM(G5:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="20">
-        <f>SUM(H5:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="20">
-        <f>SUM(I5:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="20">
-        <f>SUM(J5:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="20">
-        <f>SUM(K5:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="20">
-        <f>SUM(L5:L17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="20">
-        <f>SUM(M5:M17)</f>
-        <v/>
-      </c>
-      <c r="N18" s="20">
-        <f>SUM(B18:M18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="B22" s="20">
+        <f>SUM(B6:B15)+SUM(B17:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>SUM(C6:C15)+SUM(C17:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>SUM(D6:D15)+SUM(D17:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>SUM(E6:E15)+SUM(E17:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="20">
+        <f>SUM(F6:F15)+SUM(F17:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
+        <f>SUM(G6:G15)+SUM(G17:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="20">
+        <f>SUM(H6:H15)+SUM(H17:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="20">
+        <f>SUM(I6:I15)+SUM(I17:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="20">
+        <f>SUM(J6:J15)+SUM(J17:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="20">
+        <f>SUM(K6:K15)+SUM(K17:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="20">
+        <f>SUM(L6:L15)+SUM(L17:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="20">
+        <f>SUM(M6:M15)+SUM(M17:M21)</f>
+        <v/>
+      </c>
+      <c r="N22" s="20">
+        <f>SUM(B22:M22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B19" s="24">
-        <f>B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="24">
-        <f>B19+C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>C19+D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>D19+E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>E19+F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
-        <f>F19+G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="24">
-        <f>G19+H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
-        <f>H19+I18</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>I19+J18</f>
-        <v/>
-      </c>
-      <c r="K19" s="24">
-        <f>J19+K18</f>
-        <v/>
-      </c>
-      <c r="L19" s="24">
-        <f>K19+L18</f>
-        <v/>
-      </c>
-      <c r="M19" s="24">
-        <f>L19+M18</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>N18</f>
+      <c r="B23" s="26">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="26">
+        <f>B23+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="26">
+        <f>C23+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="26">
+        <f>D23+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="26">
+        <f>E23+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="26">
+        <f>F23+G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="26">
+        <f>G23+H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="26">
+        <f>H23+I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="26">
+        <f>I23+J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="26">
+        <f>J23+K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="26">
+        <f>K23+L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="26">
+        <f>L23+M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="26">
+        <f>N22</f>
         <v/>
       </c>
     </row>

--- a/docs/exports/pathwave_services_and_costs.xlsx
+++ b/docs/exports/pathwave_services_and_costs.xlsx
@@ -65,12 +65,12 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="001F4E78"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,7 +162,7 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -197,17 +197,32 @@
     <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -575,19 +590,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PathWave 운영비 — 연간 합계 (반복 + 초기 1회성 별도)</t>
+          <t>PathWave 운영비 — 연간 합계 (반복 + 초기 1회성 분리)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -629,7 +644,7 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>'2026년 월별'!N16</f>
+        <f>'2026년 월별'!N15</f>
         <v/>
       </c>
       <c r="C4" s="6">
@@ -638,7 +653,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>월별 반복만</t>
+          <t>월별 반복만 (매장 0→10)</t>
         </is>
       </c>
     </row>
@@ -649,7 +664,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'2027년 월별'!N16</f>
+        <f>'2027년 월별'!N15</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -658,7 +673,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>월별 반복만</t>
+          <t>월별 반복만 (매장 30→500)</t>
         </is>
       </c>
     </row>
@@ -669,7 +684,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>'초기 세팅비 (1회성)'!B22</f>
+        <f>'초기 세팅비 (1회성)'!B19</f>
         <v/>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -679,18 +694,18 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026 출시 전 한번에</t>
+          <t>Apple/Play/도메인/상표만 (Mac mini 제외)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>초기 세팅비 — 옵션 포함</t>
+          <t>초기 세팅비 — Mac mini 포함 (권장)</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>'초기 세팅비 (1회성)'!B23</f>
+        <f>'초기 세팅비 (1회성)'!B20</f>
         <v/>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -700,62 +715,73 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Mac mini + NICE 포함</t>
+          <t>+ Mac mini ₩880,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>초기 세팅비 — 전체 (NICE 포함)</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>'초기 세팅비 (1회성)'!B21</f>
+        <v/>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>+ NICE ₩100,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>2년 운영비 합계 (반복)</t>
         </is>
       </c>
-      <c r="B8" s="5">
+      <c r="B9" s="5">
         <f>B4+B5</f>
         <v/>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>2년 총합 (반복 + 필수 1회성)</t>
-        </is>
-      </c>
-      <c r="B9" s="8">
-        <f>B4+B5+B6</f>
-        <v/>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2년 총합 (반복 + Mac mini 포함)</t>
+        </is>
+      </c>
+      <c r="B10" s="8">
+        <f>B4+B5+B7</f>
+        <v/>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>전체 출시 + 2년 운영</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>주요 가정 / 변경점 (2026-05-23 v4)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>권장 셋업 기준</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>① 환율 USD 1 = ₩1,500 (이전 1,300 → 보수적 상향)</t>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>주요 가정 / 변경점 (2026-05-23 v5)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -765,7 +791,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>② 서버 = 국내 클라우드(가비아 G클라우드 또는 NHN/네이버 클라우드) — AWS 제외</t>
+          <t>① 환율 USD 1 = ₩1,500</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -775,7 +801,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>③ 도메인·이메일 분리: 패스웨이브(pathwave.co.kr) + 트리거소프트(triggersoft.kr) 2종</t>
+          <t>② 서버 = Mac mini 자체 (메모리 권장 인프라 로드맵) — Cloudflare Tunnel로 외부 노출. 비용 거의 0</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -785,7 +811,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>④ 푸시: iOS APNs 자체구축(PR #50 완성). Android는 사실상 FCM 외 대안 없음 — FCM 무료</t>
+          <t>③ 알림톡 미사용 — 자체 앱 푸시(APNs/FCM) + 이메일로 대체. 외부 카카오톡 의존 0</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -795,7 +821,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>⑤ 알림톡: 매장당 100건/월 × 9원 (현실적 가정 — 매장 100 = ₩90,000)</t>
+          <t>④ SMS 인증 옵션 — 매장 100+ 시 도입 권장 (또는 이메일 인증으로 대체)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -805,7 +831,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>⑥ 1회성 비용(Apple·Play·도메인·Mac mini·NICE·상표등록)은 월별 시트에서 제외 → 초기 세팅비 시트만</t>
+          <t>⑤ 자동화 = Mac mini 자체구축 (Python 스크립트 + cron) — Channeltalk/Make/Buffer 등 SaaS 대체</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -815,7 +841,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>⑦ 상표등록 2건(패스웨이브 + 트리거소프트) 셀프 출원 추가 (각 ₩267,000)</t>
+          <t>⑥ 던스(D-U-N-S) 무료 신청 — Apple Developer 법인 가입 선행조건 (5~10영업일)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -825,7 +851,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>⑧ 매장당 월 ₩10,000 매출 — BEP 시트 참조. 매장 100개 미만은 적자 구조</t>
+          <t>⑦ 도메인·Workspace 2계정 분리 (pathwave + triggersoft)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -835,7 +861,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>⑨ Phase 1.5 단계 추가 — 코드 완성 후 개발환경 서버 구축 + 통합 테스트 → 운영 반영</t>
+          <t>⑧ 시나리오 = 매장 수 기반 (매장당 매출 ₩10,000 직결). MAU는 매장×평균사용자 자동 계산</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -845,7 +871,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>⑩ 토스 수수료(2.9%+33원)는 매출 차감 — 운영비 미포함</t>
+          <t>⑨ 1회성 비용은 월별 시트 제외 → 초기 세팅비 시트만 (Mac mini 옵션 명시)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -855,7 +881,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>⑪ 자동화 도구(Stage 2~3)는 별도 — 출시 후 단계적 도입</t>
+          <t>⑩ Phase 1.5 단계 — Mac mini 개발환경 구축 + 통합 테스트 (운영 반영 전 필수)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -863,74 +889,14 @@
       <c r="D21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>사용 방법</t>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>⑪ ⚠ Android 푸시는 FCM 외 사실상 대안 없음 (Google Play Services 의존) — FCM 무료라 실 비용 0</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>① "서비스 신청 체크리스트": 가격 상세 + 신청 링크 + 신청 상태 드롭다운</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>② "초기 세팅비": 출시 전 1회성 — 필수만 vs 옵션 포함 두 합계</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>③ "월별 운영비 시나리오": MAU 별 반복 비용</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>④ "2026/2027년 월별": 월별 반복 비용 cash flow (1회성 제외)</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>⑤ "손익분기점 (BEP)": 매장당 1만원 매출 기준 BEP 매장 수</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>⑥ "연간 합계": 반복 + 1회성 분리 합산</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -946,21 +912,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1031,17 +997,17 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>법인 식별</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>토스페이먼츠</t>
+          <t>D-U-N-S 번호 (Apple 법인 가입 필수)</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Toss Payments</t>
+          <t>한국기업데이터(cretop) / D&amp;B</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -1051,17 +1017,17 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>거래 수수료 2.9% + 33원/건 (가입 무료)</t>
+          <t>무료 (5~10영업일)</t>
         </is>
       </c>
       <c r="G2" s="14" t="inlineStr">
         <is>
-          <t>https://merchant.tosspayments.com/</t>
+          <t>https://www.cretop.com/</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>admin@pathwave</t>
+          <t>admin@triggersoft</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr">
@@ -1076,12 +1042,12 @@
       </c>
       <c r="K2" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
-          <t>TOSS_SECRET_KEY · 심사 1~2주</t>
+          <t>Apple Developer 법인 계정 선행조건 — 무료 신청</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1057,17 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>스토어</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Apple Developer Program</t>
+          <t>토스페이먼츠</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Toss Payments</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1111,12 +1077,12 @@
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>$99/년 (₩148,500 @1500)</t>
+          <t>수수료 2.9% + 33원/건 (가입 무료)</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>https://developer.apple.com/programs/enroll/</t>
+          <t>https://merchant.tosspayments.com/</t>
         </is>
       </c>
       <c r="H3" s="13" t="inlineStr">
@@ -1136,12 +1102,12 @@
       </c>
       <c r="K3" s="16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>이메일 이관 어려움 — admin@ 필수</t>
+          <t>TOSS_SECRET_KEY · 심사 1~2주</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1122,12 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Google Play Console</t>
+          <t>Apple Developer Program (법인)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -1171,12 +1137,12 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>$25 일회성 (₩37,500 @1500)</t>
+          <t>$99/년 (₩148,500 @1500) · D-U-N-S 필요</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>https://play.google.com/console/u/0/signup</t>
+          <t>https://developer.apple.com/programs/enroll/</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -1191,15 +1157,19 @@
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="K4" s="16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>D-U-N-S 발급 후 가입 가능</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
@@ -1207,17 +1177,17 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>도메인</t>
+          <t>스토어</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>pathwave.co.kr (서비스)</t>
+          <t>Google Play Console</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>가비아</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1227,12 +1197,12 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>연 3만원 (월 ~₩2,500)</t>
+          <t>$25 일회성 (₩37,500 @1500)</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>https://www.gabia.com/</t>
+          <t>https://play.google.com/console/u/0/signup</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -1252,7 +1222,7 @@
       </c>
       <c r="K5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr"/>
@@ -1268,7 +1238,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>triggersoft.kr (법인)</t>
+          <t>pathwave.co.kr</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -1283,7 +1253,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>연 3만원 (월 ~₩2,500)</t>
+          <t>연 ~3만원 (월 ~₩2,500)</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -1293,7 +1263,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>admin@triggersoft</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1313,7 +1283,7 @@
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>법인 사업·세무·회계</t>
+          <t>서비스 도메인</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1293,17 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>도메인</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Cloudflare DNS/Tunnel</t>
+          <t>triggersoft.kr</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>가비아</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -1343,17 +1313,17 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>연 ~3만원 (월 ~₩2,500)</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>https://dash.cloudflare.com/sign-up</t>
+          <t>https://www.gabia.com/</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>admin@pathwave</t>
+          <t>admin@triggersoft</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1373,7 +1343,7 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>DNS + dev 외부 접근</t>
+          <t>법인 운영</t>
         </is>
       </c>
     </row>
@@ -1383,17 +1353,17 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>호스팅(권장)</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>가비아 G클라우드 (서버+DB)</t>
+          <t>Mac mini 자체 (Cloudflare Tunnel)</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>가비아</t>
+          <t>자체 보유</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -1403,12 +1373,12 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>월 ~5만원 (Light 통합)</t>
+          <t>월 ₩0 (전기료 ~₩3,000)</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>https://cloud.gabia.com/</t>
+          <t>https://dash.cloudflare.com/</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -1423,17 +1393,17 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-중</t>
         </is>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>국내 클라우드 — AWS 대신</t>
+          <t>메모리 권장 — Mac mini 1대로 백엔드+자동화</t>
         </is>
       </c>
     </row>
@@ -1443,17 +1413,17 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>호스팅(대안)</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>NHN Cloud (백업 옵션)</t>
+          <t>가비아 SimpleHosting Light</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>NHN Cloud</t>
+          <t>가비아</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -1463,12 +1433,12 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>월 5~7만원 (m2.c2m4)</t>
+          <t>월 ~₩4,500 (Python 지원)</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>https://www.toast.com/kr</t>
+          <t>https://www.gabia.com/service/hosting</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1483,13 +1453,13 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>검토</t>
+          <t>대안</t>
         </is>
       </c>
       <c r="K9" s="16" t="inlineStr"/>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>가비아 대체 옵션</t>
+          <t>Mac mini 부재 시 대안</t>
         </is>
       </c>
     </row>
@@ -1499,32 +1469,32 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>네이버 클라우드 (백업 옵션)</t>
+          <t>Supabase 또는 Neon (Postgres 무료)</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Naver Cloud</t>
+          <t>Supabase / Neon</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>월 3~7만원 (micro)</t>
+          <t>무료 tier (500MB ~ 1GB)</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>https://www.ncloud.com/</t>
+          <t>https://supabase.com/</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -1539,13 +1509,17 @@
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr"/>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>가비아 대체 옵션</t>
+          <t>메모리 권장 무료 tier</t>
         </is>
       </c>
     </row>
@@ -1555,17 +1529,17 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>호스팅</t>
+          <t>인증</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>프론트 정적 호스팅</t>
+          <t>Firebase Auth</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Vercel / Netlify / CFP</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1575,17 +1549,17 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>무료 tier</t>
+          <t>무료 (10K MAU)</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>https://vercel.com/signup</t>
+          <t>https://console.firebase.google.com/</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>admin@pathwave</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1605,7 +1579,7 @@
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>admin-web + provider-web</t>
+          <t>인증 전용</t>
         </is>
       </c>
     </row>
@@ -1615,17 +1589,17 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>푸시(iOS)</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Firebase Auth</t>
+          <t>APNs (자체구축)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1635,17 +1609,17 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>무료 (10K MAU)</t>
+          <t>무료 (Apple Developer 포함)</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>https://console.firebase.google.com/</t>
+          <t>https://developer.apple.com/account/resources/</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>dev@pathwave</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
@@ -1655,17 +1629,17 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>인증 전용 — 푸시는 자체구축</t>
+          <t>APNs HTTP/2 + JWT (PR #50 완성)</t>
         </is>
       </c>
     </row>
@@ -1675,17 +1649,17 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>푸시(iOS)</t>
+          <t>푸시(Android)</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>APNs (Apple Push)</t>
+          <t>FCM (무료 무제한)</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -1695,17 +1669,17 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>무료 (Apple Developer 포함)</t>
+          <t>무료 무제한</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>https://developer.apple.com/account/resources/</t>
+          <t>https://console.firebase.google.com/</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>admin@pathwave</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1715,17 +1689,17 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>자체구축 — APNs HTTP/2 + JWT (PR #50)</t>
+          <t>⚠ Android는 FCM 외 사실상 대안 없음 — Google Play Services 의존</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1709,12 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>푸시(Android)</t>
+          <t>이메일도메인</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>FCM 또는 자체 (현실 한계)</t>
+          <t>Google Workspace (Pathwave)</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -1755,17 +1729,17 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>무료 무제한</t>
+          <t>$7/계정/월 (₩10,500) + alias 4개 무료</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>https://console.firebase.google.com/</t>
+          <t>https://workspace.google.com/</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>dev@pathwave</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -1775,13 +1749,17 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr"/>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>⚠ Android 백그라운드 푸시는 FCM 외 사실상 불가 (Google Play Services 의존). 사용자 정책상 자체구축 원할 경우 in-app WebSocket fallback 만 가능</t>
+          <t>admin/dev/support/noreply/info 5메일</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1774,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace (Pathwave)</t>
+          <t>Google Workspace (Triggersoft)</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -1811,7 +1789,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>$7/계정/월 (₩10,500 @1500) + alias 4 무료</t>
+          <t>$7/계정/월 (₩10,500)</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1821,7 +1799,7 @@
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>admin@pathwave</t>
+          <t>admin@triggersoft</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
@@ -1841,7 +1819,7 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>5개 alias (admin/dev/support/noreply/info)</t>
+          <t>법인 운영</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1829,17 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>이메일도메인</t>
+          <t>상표등록</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace (Triggersoft)</t>
+          <t>상표등록 — 패스웨이브</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>특허청 (셀프 또는 변리사)</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1871,12 +1849,12 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>$7/계정/월 (₩10,500 @1500)</t>
+          <t>셀프 ~₩267,000 / 변리사 50~80만</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>https://workspace.google.com/</t>
+          <t>https://www.patent.go.kr/</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -1891,17 +1869,17 @@
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="K16" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>심사 6~12개월</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>법인 운영 1계정</t>
+          <t>출원 56,000 + 등록 211,000 (10년)</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1894,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>상표등록 — 패스웨이브</t>
+          <t>상표등록 — 트리거소프트</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -1931,7 +1909,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>셀프 약 27만원 / 변리사 위탁 50~80만원</t>
+          <t>셀프 ~₩267,000 / 변리사 50~80만</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1959,29 +1937,25 @@
           <t>심사 6~12개월</t>
         </is>
       </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>출원료 56,000 + 등록료 211,000 (10년) — 셀프</t>
-        </is>
-      </c>
+      <c r="L17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>1</v>
+      <c r="A18" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>상표등록</t>
+          <t>소셜로그인</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>상표등록 — 트리거소프트</t>
+          <t>카카오 로그인</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>특허청 (셀프 또는 변리사)</t>
+          <t>Kakao</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1991,17 +1965,17 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>셀프 약 27만원 / 변리사 위탁 50~80만원</t>
+          <t>무료</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>https://www.patent.go.kr/</t>
+          <t>https://developers.kakao.com/</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>admin@triggersoft</t>
+          <t>info@pathwave</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -2011,17 +1985,17 @@
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
-          <t>심사 6~12개월</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>법인명 상표</t>
+          <t>검수 1~2주</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2010,12 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>카카오 로그인</t>
+          <t>네이버 로그인</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Kakao</t>
+          <t>Naver</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -2056,7 +2030,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>https://developers.kakao.com/</t>
+          <t>https://developers.naver.com/</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -2076,14 +2050,10 @@
       </c>
       <c r="K19" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>검수 1~2주</t>
-        </is>
-      </c>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n">
@@ -2091,17 +2061,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>소셜로그인</t>
+          <t>이메일 발송</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>네이버 로그인</t>
+          <t>SendGrid (무료 → Essentials)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Naver</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -2111,17 +2081,17 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>무료 100통/일 · Essentials 50K/월 $19.95 (~₩30K)</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>https://developers.naver.com/</t>
+          <t>https://signup.sendgrid.com/</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>info@pathwave</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
@@ -2136,10 +2106,14 @@
       </c>
       <c r="K20" s="16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="L20" s="13" t="inlineStr"/>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>매장 100+ 시 유료 tier 필요</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n">
@@ -2147,17 +2121,17 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>알림톡/SMS</t>
+          <t>모니터링</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>솔라피 알림톡</t>
+          <t>Sentry (무료 또는 자체호스팅)</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Solapi</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -2167,12 +2141,12 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>건당 7~9원 (사용량)</t>
+          <t>무료 5K events/월 · self-hosted 무료</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>https://solapi.com/</t>
+          <t>https://sentry.io/signup/</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -2192,12 +2166,12 @@
       </c>
       <c r="K21" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>템플릿 사전심사 1~2주</t>
+          <t>대규모 시 자체 호스팅 Mac mini</t>
         </is>
       </c>
     </row>
@@ -2207,237 +2181,225 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>알림톡/SMS</t>
+          <t>지도</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>솔라피 SMS 인증</t>
+          <t>Google Maps API</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>월 $200 무료 크레딧</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>https://console.cloud.google.com/</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>dev@pathwave</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>카드 등록 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>SMS 인증(옵션)</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>솔라피 SMS</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
           <t>Solapi</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>건당 8~15원 (LMS 28~35원)</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>건당 8~15원 (LMS 28~35원) · 사용량 기반</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>https://solapi.com/</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>dev@pathwave</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>회원가입 인증</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>이메일</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>SendGrid</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>무료 100통/일</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>https://signup.sendgrid.com/</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>대안</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>이메일 인증으로 대체 가능 — 매장 100+ 시 도입</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>알림톡(옵션)</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>솔라피 알림톡</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Solapi</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>건당 7~9원 · 카카오톡 채널 필요</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>https://solapi.com/</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>dev@pathwave</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>발신: support@</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>모니터링</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Sentry</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Sentry</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>무료 5K events/월</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>https://sentry.io/signup/</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>dev@pathwave</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>대안</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr"/>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>⚠ 자체 앱 푸시 + 이메일로 대체 가능 — 외부 의존 줄이려면 미도입</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>본인인증</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>NICE / KCB / PASS</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>본인인증 사업자</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>보증금 ~10만원 + 건당 30~80원</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>https://www.niceinfo.co.kr/</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>admin@pathwave</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>백엔드 통합 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>지도</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Google Maps API</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>월 $200 무료 크레딧</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>https://console.cloud.google.com/</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>dev@pathwave</t>
-        </is>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
+          <t>6/말~7/중</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr"/>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>카드 등록 필수</t>
+          <t>미성년자 확인 (대체 불가)</t>
         </is>
       </c>
     </row>
@@ -2447,17 +2409,17 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>본인인증</t>
+          <t>번역</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>NICE / KCB / PASS</t>
+          <t>DeepL Pro</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>본인인증 사업자</t>
+          <t>DeepL</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -2467,17 +2429,17 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>계약 보증금 ~10만원 + 건당 30~80원</t>
+          <t>무료 500K chars/월 · Starter ~€5/월</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.niceinfo.co.kr/</t>
+          <t>https://www.deepl.com/pro</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>admin@pathwave</t>
+          <t>dev@pathwave</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
@@ -2487,7 +2449,7 @@
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>2026-06-말</t>
+          <t>2026-07-초</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
@@ -2497,7 +2459,7 @@
       </c>
       <c r="L26" s="13" t="inlineStr">
         <is>
-          <t>미성년자 확인</t>
+          <t>P8b 채팅 자동번역 USP</t>
         </is>
       </c>
     </row>
@@ -2507,32 +2469,32 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>번역</t>
+          <t>자동화(자체)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>DeepL Pro</t>
+          <t>챗봇·이메일·SNS 게시 — Mac mini 자체구축</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>DeepL</t>
+          <t>Mac mini</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>필수</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>무료 500K chars/월 / Starter ~€5/월</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>https://www.deepl.com/pro</t>
+          <t>월 ₩0 (전기 + 개발 시간)</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -2547,17 +2509,13 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-초</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-중</t>
-        </is>
-      </c>
+          <t>출시 후</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr"/>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>P8b 채팅 자동번역 USP</t>
+          <t>메모리 권장 — Python 스크립트 + cron + 카카오 i 오픈빌더 webhook</t>
         </is>
       </c>
     </row>
@@ -2567,17 +2525,17 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>번역</t>
+          <t>자동화(옵션)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Google Translate (대안)</t>
+          <t>ChatGPT API (소규모 AI 응답)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -2587,12 +2545,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>$20/1M chars</t>
+          <t>$0.15~3/M tokens (사용량)</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://console.cloud.google.com/</t>
+          <t>https://platform.openai.com/signup</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -2611,7 +2569,11 @@
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr"/>
-      <c r="L28" s="13" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>Mac mini Llama 양자화 자체 LLM 대체 가능</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
@@ -2619,17 +2581,17 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>자동화 S2</t>
+          <t>자동화(옵션)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Channeltalk</t>
+          <t>Twilio Voice (AI 음성)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Channel.io</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -2639,17 +2601,17 @@
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>무료~5만원/월</t>
+          <t>분당 100~500원</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://channel.io/ko</t>
+          <t>https://www.twilio.com/</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>dev@pathwave</t>
+          <t>admin@pathwave</t>
         </is>
       </c>
       <c r="I29" s="15" t="inlineStr">
@@ -2659,292 +2621,20 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>출시 후</t>
+          <t>+3개월</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr"/>
-      <c r="L29" s="13" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>자동화 S2</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>ChatGPT API</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>$0.15~3/M tokens</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>https://platform.openai.com/signup</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>dev@pathwave</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>출시 후</t>
-        </is>
-      </c>
-      <c r="K30" s="16" t="inlineStr"/>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>응대 자동화</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>자동화 S2</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Make.com</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Make</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>무료~$9~30/월</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>https://www.make.com/en/register</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>dev@pathwave</t>
-        </is>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>출시 후</t>
-        </is>
-      </c>
-      <c r="K31" s="16" t="inlineStr"/>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>노코드 허브</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>자동화 S2</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Buffer / Metricool</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Buffer / Metricool</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>$6~15/월</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>https://buffer.com/pricing</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>info@pathwave</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>출시 후</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="inlineStr"/>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>SNS 자동</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>자동화 S3</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>HubSpot CRM</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>HubSpot</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>$20~50/월</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>https://www.hubspot.com/</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>admin@pathwave</t>
-        </is>
-      </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>+3개월</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr"/>
-      <c r="L33" s="13" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>자동화 S2</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Twilio Voice</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>분당 100~500원</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.twilio.com/</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>admin@pathwave</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>+3개월</t>
-        </is>
-      </c>
-      <c r="K34" s="16" t="inlineStr"/>
-      <c r="L34" s="13" t="inlineStr">
-        <is>
-          <t>AI 음성</t>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>Stage 2 — 070 회선 후 도입</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"대기,신청중,검수중,활성,검토,대안,보류"</formula1>
+    <dataValidation sqref="I2:I29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"대기,신청중,검수중,활성,대안,보류"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -2973,14 +2663,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2992,19 +2676,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>초기 세팅비 — 출시 전 1회성 / 연 1회 비용 (월별 시트에 분산 안 함)</t>
+          <t>초기 세팅비 — 출시 전 1회성 / 연 1회 (월별 시트에 분산 안 함)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3042,67 +2726,67 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Apple Developer Program — 첫 회비</t>
+          <t>D-U-N-S 번호 신청 (한국기업데이터)</t>
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>148500</v>
+        <v>0</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>연 1회</t>
+          <t>일회성</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>$99 × 1500</t>
+          <t>무료 — Apple 법인 가입 선행, 5~10영업일</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Google Play Console — 등록비</t>
+          <t>Apple Developer Program — 첫 회비</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>37500</v>
+        <v>148500</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>일회성</t>
+          <t>연 1회</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>$25 일회성</t>
+          <t>$99 × 1500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>도메인 — pathwave.co.kr</t>
+          <t>Google Play Console — 등록비</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>30000</v>
+        <v>37500</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>연 1회</t>
+          <t>일회성</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>서비스 도메인 (가비아)</t>
+          <t>$25 일회성</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>도메인 — triggersoft.kr</t>
+          <t>도메인 — pathwave.co.kr</t>
         </is>
       </c>
       <c r="B7" s="19" t="n">
@@ -3115,34 +2799,34 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>법인 도메인 (가비아)</t>
+          <t>서비스 도메인 (가비아)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>상표등록 — 패스웨이브 (셀프 출원)</t>
+          <t>도메인 — triggersoft.kr</t>
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>267000</v>
+        <v>30000</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>일회성</t>
+          <t>연 1회</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>출원 56,000 + 등록 211,000 (10년) — 변리사 위탁 시 50~80만</t>
+          <t>법인 도메인 (가비아)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>상표등록 — 트리거소프트 (셀프 출원)</t>
+          <t>상표등록 — 패스웨이브 (셀프 출원)</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
@@ -3155,18 +2839,18 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>동일 — 법인명 상표</t>
+          <t>출원 56,000 + 등록 211,000 (10년 갱신)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Mac mini M1 16GB/256GB 중고 (선택)</t>
+          <t>상표등록 — 트리거소프트 (셀프 출원)</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>800000</v>
+        <v>267000</v>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
@@ -3175,18 +2859,18 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>자본 여유 시 — 24/7 운영 베이스</t>
+          <t>법인명 상표</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Mac mini 주변기기 (외장 SSD 등, 선택)</t>
+          <t>Mac mini M1 16GB 중고 (운영 베이스)</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>80000</v>
+        <v>800000</v>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
@@ -3195,18 +2879,18 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Mac mini 옵션 시</t>
+          <t>자체 호스팅 + 자동화 — 메모리 권장</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>NICE 본인인증 — 계약 보증금 (선택)</t>
+          <t>Mac mini 주변기기 (외장 SSD)</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
@@ -3215,18 +2899,18 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>미성년자 확인 도입 시</t>
+          <t>Mac mini 옵션</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>카카오 로그인 검수</t>
+          <t>NICE 본인인증 — 보증금 (선택)</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
@@ -3235,14 +2919,14 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>무료, 1~2주</t>
+          <t>미성년자 확인 도입 시</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>네이버 로그인 가입</t>
+          <t>카카오 / 네이버 로그인 검수</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
@@ -3255,14 +2939,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>무료, 1~2주</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>솔라피 알림톡 템플릿 등록·심사</t>
+          <t>솔라피 알림톡 템플릿 등록 (도입 시)</t>
         </is>
       </c>
       <c r="B15" s="19" t="n">
@@ -3302,7 +2986,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>사업자등록 (홈택스)</t>
+          <t>사업자등록 / 통신판매업 / 위치기반신고</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
@@ -3322,7 +3006,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>통신판매업 신고</t>
+          <t>Cloudflare / Firebase / Sentry 가입</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
@@ -3340,92 +3024,53 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>위치기반서비스사업 신고</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>소계 — 필수만 (Mac mini·NICE 제외)</t>
+        </is>
+      </c>
+      <c r="B19" s="21">
+        <f>SUM(B4:B9)+B14+SUM(B15:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="13" t="inlineStr"/>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>무료, 수 주 소요</t>
+          <t>Apple/Play/도메인/상표만</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Cloudflare / Firebase / Sentry 가입</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>소계 — Mac mini 포함 (메모리 권장)</t>
+        </is>
+      </c>
+      <c r="B20" s="21">
+        <f>SUM(B4:B9)+SUM(B11:B12)+B14+SUM(B15:B18)</f>
+        <v/>
+      </c>
+      <c r="C20" s="13" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>+ Mac mini 880,000</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Google Workspace 초기 셋업</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>일회성</t>
-        </is>
-      </c>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>소계 — 전체 (옵션 모두 포함)</t>
+        </is>
+      </c>
+      <c r="B21" s="21">
+        <f>SUM(B4:B18)</f>
+        <v/>
+      </c>
+      <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>월 정액에 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>소계 — 필수만 (Mac mini·NICE 제외)</t>
-        </is>
-      </c>
-      <c r="B22" s="21">
-        <f>SUM(B4:B9)+SUM(B14:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>소계 — 옵션 포함 (Mac mini + NICE)</t>
-        </is>
-      </c>
-      <c r="B23" s="21">
-        <f>SUM(B4:B21)</f>
-        <v/>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>전체 포함</t>
+          <t>+ NICE 100,000</t>
         </is>
       </c>
     </row>
@@ -3443,26 +3088,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>월별 운영비 시나리오 — 반복 비용만 (1회성 제외)</t>
+          <t>월별 운영비 시나리오 — 매장 수 기반 (자체구축 우선, 외부는 옵션)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -3470,288 +3117,471 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>매장당 평균 사용자 (가정)</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>매장당 매출 (가정, ₩/월)</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>MAU 1K (매장 10)</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>MAU 10K (매장 100)</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>MAU 100K (매장 500)</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>매장 10 (초기)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>매장 100 (Y1 목표)</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>매장 500 (Y2~3)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>매장 1000 (Y3+)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>서버 (가비아 G클라우드)</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D4" s="19" t="n">
-        <v>600000</v>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>국내 — Light → Standard → 분리·HA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>DB (PG 통합/분리)</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>초기 서버 포함 → MAU 10K부터 분리</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>도메인 (2개 × 월할)</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>pathwave + triggersoft</t>
-        </is>
-      </c>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>매장 수</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>알림톡 (매장당 100건/월 × 9원)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>450000</v>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>매장 × 100건 × 9원</t>
-        </is>
-      </c>
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>MAU (매장×평균)</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>B6*$B$3</f>
+        <v/>
+      </c>
+      <c r="C7" s="26">
+        <f>C6*$B$3</f>
+        <v/>
+      </c>
+      <c r="D7" s="26">
+        <f>D6*$B$3</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>E6*$B$3</f>
+        <v/>
+      </c>
+      <c r="F7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>SMS + 본인인증</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>회원가입·결제</t>
-        </is>
-      </c>
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>월 매출 (매장×$E$3)</t>
+        </is>
+      </c>
+      <c r="B8" s="27">
+        <f>B6*$E$3</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
+        <f>C6*$E$3</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>D6*$E$3</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>E6*$E$3</f>
+        <v/>
+      </c>
+      <c r="F8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>서버 (Mac mini 자체, 전기)</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>무료 100통/일</t>
+        <v>3000</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>메모리 권장 — Cloudflare Tunnel</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace (2계정 × $7)</t>
+          <t>서버 확장 (대안: 가비아/VPS)</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>pathwave + triggersoft @1500</t>
+        <v>30000</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>매장 500+ 시 부하 분산 필요 시</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Sentry 모니터링</t>
+          <t>도메인 (2개 × 월할)</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>무료 5K → 대규모 유료</t>
+        <v>5000</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>pathwave + triggersoft</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Firebase Auth</t>
+          <t>Workspace (2계정 × $7 = ₩21K)</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>무료 10K MAU → 초과 유료</t>
-        </is>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Google Maps (초과분)</t>
+          <t>이메일 (SendGrid)</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>월 $200 크레딧</t>
+      <c r="E13" s="19" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>무료→Essentials $20→Pro $90 (매장 1K=10K통/월 이상)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>푸시 (APNs + FCM — 무료)</t>
+          <t>SMS 인증 (옵션 — 이메일 인증 대체 가능)</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>APNs 자체구축 + FCM 무료</t>
+        <v>30000</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>솔라피 — 또는 이메일 인증으로 대체</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>알림톡 (옵션 — 자체 푸시로 대체 가능)</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>⚠ 카카오톡 채널 운영 시만 — 자체 푸시/이메일이면 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Firebase Auth (10K MAU 무료)</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>매장 1K(MAU 50K)에서 일부 유료</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Google Maps (월 $200 무료)</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>대규모 트래픽 시 초과분</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>모니터링 (Sentry 무료 / 자체)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>자체 호스팅 시 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>번역 API (P8b)</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>DeepL — 채팅 자동 번역</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>자동화 (Mac mini 자체)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>메모리 — Python 스크립트</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>월 운영비 합계</t>
         </is>
       </c>
-      <c r="B15" s="21">
-        <f>SUM(B4:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="21">
-        <f>SUM(C4:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="21">
-        <f>SUM(D4:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="13" t="inlineStr"/>
+      <c r="B21" s="21">
+        <f>SUM(B9:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="21">
+        <f>SUM(C9:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>SUM(D9:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
+        <f>SUM(E9:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>월 손익 (매출 − 비용)</t>
+        </is>
+      </c>
+      <c r="B22" s="29">
+        <f>B8-B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="29">
+        <f>C8-C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>D8-D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>E8-E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3763,10 +3593,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -3776,7 +3606,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>손익분기점 — 매장당 월 ₩10,000 매출 가정</t>
+          <t>손익분기점 — 매장 수가 매출 단위</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3799,40 +3629,40 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>월 운영비 (₩)</t>
+          <t>월 운영비</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>매장 수</t>
+          <t>매장 수 (실제)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>월 매출 (₩)</t>
+          <t>월 매출</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>월 손익 (₩)</t>
+          <t>월 손익</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>MAU 1K (매장 10)</t>
+          <t>매장 10 (초기)</t>
         </is>
       </c>
       <c r="B4" s="5">
-        <f>'월별 운영비 시나리오'!B15</f>
-        <v/>
-      </c>
-      <c r="C4" s="22" t="n">
+        <f>'월별 운영비 시나리오'!B21</f>
+        <v/>
+      </c>
+      <c r="C4" s="30" t="n">
         <v>10</v>
       </c>
       <c r="D4" s="6">
-        <f>C4*10000</f>
+        <f>C4*'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
       <c r="E4" s="8">
@@ -3843,18 +3673,18 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MAU 10K (매장 100)</t>
+          <t>매장 100 (Y1 목표)</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'월별 운영비 시나리오'!C15</f>
-        <v/>
-      </c>
-      <c r="C5" s="22" t="n">
+        <f>'월별 운영비 시나리오'!C21</f>
+        <v/>
+      </c>
+      <c r="C5" s="30" t="n">
         <v>100</v>
       </c>
       <c r="D5" s="6">
-        <f>C5*10000</f>
+        <f>C5*'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
       <c r="E5" s="8">
@@ -3865,18 +3695,18 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>MAU 100K (매장 500)</t>
+          <t>매장 500 (Y2~3)</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>'월별 운영비 시나리오'!D15</f>
-        <v/>
-      </c>
-      <c r="C6" s="22" t="n">
+        <f>'월별 운영비 시나리오'!D21</f>
+        <v/>
+      </c>
+      <c r="C6" s="30" t="n">
         <v>500</v>
       </c>
       <c r="D6" s="6">
-        <f>C6*10000</f>
+        <f>C6*'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
       <c r="E6" s="8">
@@ -3885,63 +3715,71 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>매장 1000 (Y3+)</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>'월별 운영비 시나리오'!E21</f>
+        <v/>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="6">
+        <f>C7*'월별 운영비 시나리오'!$E$3</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>D7-B7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>손익분기 매장 수 (각 시나리오)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>MAU 1K 운영비 → BEP 매장 수</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <f>B4/10000</f>
-        <v/>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>운영비 ÷ 1만원</t>
-        </is>
-      </c>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>BEP 매장 수 (운영비 ÷ 매장당 매출)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>MAU 10K 운영비 → BEP 매장 수</t>
-        </is>
-      </c>
-      <c r="B10" s="23">
-        <f>B5/10000</f>
+          <t>매장 10 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B10" s="31">
+        <f>B4/'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>운영비 ÷ 1만원</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>MAU 100K 운영비 → BEP 매장 수</t>
-        </is>
-      </c>
-      <c r="B11" s="23">
-        <f>B6/10000</f>
+          <t>매장 100 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B11" s="31">
+        <f>B5/'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -3949,31 +3787,37 @@
       <c r="E11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>⚠ 매장당 월 1만원 매출 — 구조적 손익 분석 필요</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>매장 500 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B12" s="31">
+        <f>B6/'월별 운영비 시나리오'!$E$3</f>
+        <v/>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>· 매장당 매출 1만원은 인건비·자본비용 미반영 시점. 손익분기는 비용 회수만 의미</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>매장 1000 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>B7/'월별 운영비 시나리오'!$E$3</f>
+        <v/>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>· 매장 100개 미달 시 적자 — 초기에는 자본 투자 + B2B 영업 + 광고/스폰서 등 보완 매출 필요</t>
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 수익 구조 분석</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -3984,7 +3828,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>· 매장 증가 = 알림톡·SMS 사용량 증가 (비례) → 단가 협상력 필요</t>
+          <t>· 매장당 월 ₩10,000 매출 — Y1 목표 100매장 = ₩1M/월 매출, 운영비 ~₩60K → 순익 ₩940K/월</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -3995,7 +3839,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>· 자동화(Stage 2~3) 도구 도입 시 인건비 절감 효과로 BEP 낮춤</t>
+          <t>· Mac mini 자체구축 + 자체 푸시·이메일로 운영비 대폭 절감</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -4006,13 +3850,57 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>· 추후 부가 수익원(번역 API 유료 / 광고 / 데이터 분석 등) 검토 필요</t>
+          <t>· 알림톡(카카오) 제거 시 외부 의존 0 — 단 솔라피 SMS 인증은 매장 100+ 시 도입 권장(또는 이메일 인증)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>· Firebase Auth는 10K MAU 무료 — 매장 1K (MAU 50K) 도달 시 일부 유료 전환</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>· 자동화는 Mac mini 자체 Python 스크립트 (메모리 권장) — 외부 SaaS 비용 0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>· Stage 2~3 도구(Twilio·번역·자동화 SaaS)는 매출 5~10% 재투자 원칙</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>· 초기 세팅비 회수 — 매장 100 시나리오 순익 ₩940K/월 → 셋업비(필수) ~₩780K 1개월 회수</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4028,10 +3916,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -4050,7 +3938,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026년 월별 운영비 (반복 비용만 — 1회성은 초기 세팅비 시트 참조)</t>
+          <t>2026년 월별 운영비 (반복 비용만 — 1회성은 초기 세팅비 시트)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4068,9 +3956,9 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>※ 출시 = 2026-07 하순~08-초. 1~5월 코드 작업(비용 0). 6월 외부 신청 시작(도메인·Workspace). 7월 서버 셋업 + Apple/Google Play(1회성은 별도). 8월 출시 후 MAU 0~1K, 매장 0→10</t>
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>※ 6/2주 외부 신청 시작. Mac mini 7월 셋업 (자체 호스팅 + Cloudflare Tunnel). 8월 출시 후 매장 0→10. 알림톡/카카오톡 미사용 — 자체 푸시·이메일로 대체</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -4178,7 +4066,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>서버 (가비아 G클라우드)</t>
+          <t>서버 (Mac mini 자체)</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
@@ -4200,24 +4088,24 @@
         <v>0</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N5" s="26">
+        <v>3000</v>
+      </c>
+      <c r="N5" s="34">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
@@ -4225,7 +4113,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>DB (PG)</t>
+          <t>도메인 (월할)</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
@@ -4244,27 +4132,27 @@
         <v>0</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="26">
+        <v>5000</v>
+      </c>
+      <c r="N6" s="34">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -4272,7 +4160,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>도메인 (월할)</t>
+          <t>Workspace (2계정)</t>
         </is>
       </c>
       <c r="B7" s="19" t="n">
@@ -4291,27 +4179,27 @@
         <v>0</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N7" s="26">
+        <v>21000</v>
+      </c>
+      <c r="N7" s="34">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -4319,7 +4207,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>알림톡 (사용량)</t>
+          <t>이메일 (SendGrid)</t>
         </is>
       </c>
       <c r="B8" s="19" t="n">
@@ -4344,21 +4232,21 @@
         <v>0</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>9000</v>
-      </c>
-      <c r="N8" s="26">
+        <v>0</v>
+      </c>
+      <c r="N8" s="34">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -4366,7 +4254,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>SMS + 본인인증</t>
+          <t>SMS 인증 (옵션)</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
@@ -4391,13 +4279,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="19" t="n">
         <v>2000</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="K9" s="19" t="n">
         <v>3000</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>4000</v>
       </c>
       <c r="L9" s="19" t="n">
         <v>5000</v>
@@ -4405,7 +4293,7 @@
       <c r="M9" s="19" t="n">
         <v>5000</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="34">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -4413,7 +4301,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>Firebase Auth (초과)</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
@@ -4452,7 +4340,7 @@
       <c r="M10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="34">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -4460,7 +4348,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace (2계정)</t>
+          <t>Google Maps (초과)</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
@@ -4479,27 +4367,27 @@
         <v>0</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>21000</v>
-      </c>
-      <c r="N11" s="26">
+        <v>0</v>
+      </c>
+      <c r="N11" s="34">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -4546,7 +4434,7 @@
       <c r="M12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -4554,7 +4442,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Firebase Auth</t>
+          <t>번역 API (P8b)</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
@@ -4593,7 +4481,7 @@
       <c r="M13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -4601,7 +4489,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Google Maps (초과)</t>
+          <t>서버 확장 (대안)</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
@@ -4640,173 +4528,126 @@
       <c r="M14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="34">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>번역 API (P8b)</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="26">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>월 운영비 합계</t>
+        </is>
+      </c>
+      <c r="B15" s="21">
+        <f>SUM(B5:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="21">
+        <f>SUM(C5:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>SUM(D5:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>SUM(E5:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>SUM(F5:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>SUM(I5:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="21">
+        <f>SUM(J5:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>SUM(K5:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="21">
+        <f>SUM(L5:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="21">
+        <f>SUM(M5:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="21">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>월 운영비 합계 (반복만)</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>SUM(B5:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="21">
-        <f>SUM(C5:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E5:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="21">
-        <f>SUM(F5:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="21">
-        <f>SUM(G5:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="21">
-        <f>SUM(H5:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>SUM(I5:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="21">
-        <f>SUM(J5:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="21">
-        <f>SUM(K5:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="21">
-        <f>SUM(L5:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="21">
-        <f>SUM(M5:M15)</f>
-        <v/>
-      </c>
-      <c r="N16" s="21">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B17" s="28">
-        <f>B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="28">
-        <f>B17+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="28">
-        <f>C17+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="28">
-        <f>D17+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="28">
-        <f>E17+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="28">
-        <f>F17+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="28">
-        <f>G17+H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="28">
-        <f>H17+I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="28">
-        <f>I17+J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="28">
-        <f>J17+K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="28">
-        <f>K17+L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="28">
-        <f>L17+M16</f>
-        <v/>
-      </c>
-      <c r="N17" s="28">
-        <f>N16</f>
+      <c r="B16" s="27">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="27">
+        <f>B16+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>C16+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>D16+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>E16+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="27">
+        <f>F16+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>G16+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="27">
+        <f>H16+I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="27">
+        <f>I16+J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="27">
+        <f>J16+K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="27">
+        <f>K16+L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="27">
+        <f>L16+M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="27">
+        <f>N15</f>
         <v/>
       </c>
     </row>
@@ -4825,10 +4666,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -4847,7 +4688,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2027년 월별 운영비 (반복 비용만 — 1회성은 초기 세팅비 시트 참조)</t>
+          <t>2027년 월별 운영비 (반복 비용만 — 1회성은 초기 세팅비 시트)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4865,9 +4706,9 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>※ 점진 성장 — Q1: 매장 20~30(MAU 1~2K), Q2: 50(MAU 3~5K), Q3: 100(MAU 5~10K), Q4: 200(MAU 10K+). 알림톡 = 매장당 100건/월 × 9원</t>
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>※ Q1 매장 ~30, Q2 ~100, Q3 ~300, Q4 ~500. Mac mini 자체 호스팅 + 자동화. 이메일 Q2부터 SendGrid Essentials. 알림톡 미사용 — 자체 푸시 + 이메일</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -4975,46 +4816,46 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>서버 (가비아 G클라우드)</t>
+          <t>서버 (Mac mini 자체)</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>80000</v>
+        <v>3000</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>80000</v>
+        <v>3000</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>80000</v>
+        <v>3000</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>120000</v>
+        <v>3000</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>120000</v>
+        <v>3000</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>120000</v>
+        <v>3000</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>150000</v>
+        <v>3000</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>150000</v>
+        <v>3000</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>150000</v>
-      </c>
-      <c r="N5" s="26">
+        <v>3000</v>
+      </c>
+      <c r="N5" s="34">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
@@ -5022,46 +4863,46 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>DB (PG)</t>
+          <t>도메인 (월할)</t>
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="L6" s="19" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="M6" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="N6" s="26">
+        <v>5000</v>
+      </c>
+      <c r="N6" s="34">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -5069,46 +4910,46 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>도메인 (월할)</t>
+          <t>Workspace (2계정)</t>
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N7" s="26">
+        <v>21000</v>
+      </c>
+      <c r="N7" s="34">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -5116,46 +4957,46 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>알림톡 (사용량)</t>
+          <t>이메일 (SendGrid)</t>
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>22500</v>
+        <v>0</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>40500</v>
+        <v>30000</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>63000</v>
+        <v>30000</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>72000</v>
+        <v>30000</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>135000</v>
+        <v>30000</v>
       </c>
       <c r="L8" s="19" t="n">
-        <v>153000</v>
+        <v>30000</v>
       </c>
       <c r="M8" s="19" t="n">
-        <v>180000</v>
-      </c>
-      <c r="N8" s="26">
+        <v>30000</v>
+      </c>
+      <c r="N8" s="34">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -5163,46 +5004,46 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>SMS + 본인인증</t>
+          <t>SMS 인증 (옵션)</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
         <v>5000</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>22000</v>
+        <v>30000</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>45000</v>
-      </c>
-      <c r="N9" s="26">
+        <v>50000</v>
+      </c>
+      <c r="N9" s="34">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -5210,7 +5051,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>Firebase Auth (초과)</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
@@ -5226,30 +5067,30 @@
         <v>0</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="L10" s="19" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M10" s="19" t="n">
-        <v>12000</v>
-      </c>
-      <c r="N10" s="26">
+        <v>30000</v>
+      </c>
+      <c r="N10" s="34">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -5257,46 +5098,46 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Google Workspace (2계정)</t>
+          <t>Google Maps (초과)</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="19" t="n">
-        <v>21000</v>
+        <v>10000</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>21000</v>
-      </c>
-      <c r="N11" s="26">
+        <v>20000</v>
+      </c>
+      <c r="N11" s="34">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -5332,18 +5173,18 @@
         <v>0</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="M12" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -5351,7 +5192,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Firebase Auth</t>
+          <t>번역 API (P8b)</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
@@ -5364,33 +5205,33 @@
         <v>0</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>15000</v>
+        <v>60000</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>20000</v>
-      </c>
-      <c r="N13" s="26">
+        <v>80000</v>
+      </c>
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -5398,7 +5239,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Google Maps (초과)</t>
+          <t>서버 확장 (대안)</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
@@ -5423,187 +5264,140 @@
         <v>0</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="J14" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="M14" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="N14" s="26">
+        <v>50000</v>
+      </c>
+      <c r="N14" s="34">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>번역 API (P8b)</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>40000</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L15" s="19" t="n">
-        <v>60000</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>80000</v>
-      </c>
-      <c r="N15" s="26">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>월 운영비 합계</t>
+        </is>
+      </c>
+      <c r="B15" s="21">
+        <f>SUM(B5:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="21">
+        <f>SUM(C5:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>SUM(D5:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>SUM(E5:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>SUM(F5:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>SUM(I5:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="21">
+        <f>SUM(J5:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>SUM(K5:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="21">
+        <f>SUM(L5:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="21">
+        <f>SUM(M5:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="21">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>월 운영비 합계 (반복만)</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>SUM(B5:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="21">
-        <f>SUM(C5:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>SUM(E5:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="21">
-        <f>SUM(F5:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="21">
-        <f>SUM(G5:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="21">
-        <f>SUM(H5:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>SUM(I5:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="21">
-        <f>SUM(J5:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="21">
-        <f>SUM(K5:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="21">
-        <f>SUM(L5:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="21">
-        <f>SUM(M5:M15)</f>
-        <v/>
-      </c>
-      <c r="N16" s="21">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B17" s="28">
-        <f>B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="28">
-        <f>B17+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="28">
-        <f>C17+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="28">
-        <f>D17+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="28">
-        <f>E17+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="28">
-        <f>F17+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="28">
-        <f>G17+H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="28">
-        <f>H17+I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="28">
-        <f>I17+J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="28">
-        <f>J17+K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="28">
-        <f>K17+L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="28">
-        <f>L17+M16</f>
-        <v/>
-      </c>
-      <c r="N17" s="28">
-        <f>N16</f>
+      <c r="B16" s="27">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="27">
+        <f>B16+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>C16+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>D16+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>E16+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="27">
+        <f>F16+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>G16+H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="27">
+        <f>H16+I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="27">
+        <f>I16+J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="27">
+        <f>J16+K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="27">
+        <f>K16+L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="27">
+        <f>L16+M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="27">
+        <f>N15</f>
         <v/>
       </c>
     </row>

--- a/docs/exports/pathwave_services_and_costs.xlsx
+++ b/docs/exports/pathwave_services_and_costs.xlsx
@@ -91,7 +91,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +123,11 @@
         <fgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4E1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -203,10 +208,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3088,7 +3099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3126,7 +3137,7 @@
         </is>
       </c>
       <c r="B3" s="23" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="22" t="inlineStr">
@@ -3140,305 +3151,305 @@
       <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>매장당 비콘 개수 (가정)</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>비콘 단가 (₩/개, 배송 포함)</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>매장 10 (초기)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>매장 100 (Y1 목표)</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>매장 500 (Y2~3)</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>매장 1000 (Y3+)</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>매장 10,000 (Y1 목표)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>매장 30,000 (Y2~3)</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>매장 70,000 (Y3+)</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>매장 수</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>MAU (매장×평균)</t>
-        </is>
-      </c>
-      <c r="B7" s="26">
-        <f>B6*$B$3</f>
-        <v/>
-      </c>
-      <c r="C7" s="26">
-        <f>C6*$B$3</f>
-        <v/>
-      </c>
-      <c r="D7" s="26">
-        <f>D6*$B$3</f>
-        <v/>
-      </c>
-      <c r="E7" s="26">
-        <f>E6*$B$3</f>
-        <v/>
+          <t>매장 수</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>70000</v>
       </c>
       <c r="F7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>월 매출 (매장×$E$3)</t>
+          <t>MAU (매장×평균)</t>
         </is>
       </c>
       <c r="B8" s="27">
-        <f>B6*$E$3</f>
+        <f>B7*$B$3</f>
         <v/>
       </c>
       <c r="C8" s="27">
-        <f>C6*$E$3</f>
+        <f>C7*$B$3</f>
         <v/>
       </c>
       <c r="D8" s="27">
-        <f>D6*$E$3</f>
+        <f>D7*$B$3</f>
         <v/>
       </c>
       <c r="E8" s="27">
-        <f>E6*$E$3</f>
+        <f>E7*$B$3</f>
         <v/>
       </c>
       <c r="F8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>서버 (Mac mini 자체, 전기)</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>메모리 권장 — Cloudflare Tunnel</t>
-        </is>
-      </c>
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>월 매출 (매장×매장당매출)</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
+        <f>B7*$E$3</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>C7*$E$3</f>
+        <v/>
+      </c>
+      <c r="D9" s="28">
+        <f>D7*$E$3</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>E7*$E$3</f>
+        <v/>
+      </c>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>서버 확장 (대안: 가비아/VPS)</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>100000</v>
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>비콘 누적 CAPEX (매장×개수×단가)</t>
+        </is>
+      </c>
+      <c r="B10" s="29">
+        <f>B7*$B$4*$E$4</f>
+        <v/>
+      </c>
+      <c r="C10" s="29">
+        <f>C7*$B$4*$E$4</f>
+        <v/>
+      </c>
+      <c r="D10" s="29">
+        <f>D7*$B$4*$E$4</f>
+        <v/>
+      </c>
+      <c r="E10" s="29">
+        <f>E7*$B$4*$E$4</f>
+        <v/>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>매장 500+ 시 부하 분산 필요 시</t>
+          <t>매장 가입 시 1회 — 매장당 매출 ₩10K 기준 2개월 회수</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>도메인 (2개 × 월할)</t>
+          <t>서버 (Mac mini 자체, 전기)</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>pathwave + triggersoft</t>
+          <t>메모리 권장 — Cloudflare Tunnel</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Workspace (2계정 × $7 = ₩21K)</t>
+          <t>서버 확장 (대안: 가비아/VPS)</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>21000</v>
+        <v>30000</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>21000</v>
-      </c>
-      <c r="F12" s="13" t="inlineStr"/>
+        <v>100000</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>매장 500+ 시 부하 분산 필요 시</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>이메일 (SendGrid)</t>
+          <t>도메인 (2개 × 월할)</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>135000</v>
+        <v>5000</v>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>무료→Essentials $20→Pro $90 (매장 1K=10K통/월 이상)</t>
+          <t>pathwave + triggersoft</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>SMS 인증 (옵션 — 이메일 인증 대체 가능)</t>
+          <t>Workspace (2계정 × $7 = ₩21K)</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>30000</v>
+        <v>21000</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>솔라피 — 또는 이메일 인증으로 대체</t>
-        </is>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="F14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>알림톡 (옵션 — 자체 푸시로 대체 가능)</t>
+          <t>이메일 (SendGrid)</t>
         </is>
       </c>
       <c r="B15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>⚠ 카카오톡 채널 운영 시만 — 자체 푸시/이메일이면 0</t>
+          <t>무료→Essentials $20→Pro $90 (매장 1K=10K통/월 이상)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Firebase Auth (10K MAU 무료)</t>
+          <t>SMS 인증 (옵션 — 이메일 인증 대체 가능)</t>
         </is>
       </c>
       <c r="B16" s="19" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>매장 1K(MAU 50K)에서 일부 유료</t>
+          <t>솔라피 — 또는 이메일 인증으로 대체</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Google Maps (월 $200 무료)</t>
+          <t>알림톡 (옵션 — 자체 푸시로 대체 가능)</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
@@ -3451,18 +3462,18 @@
         <v>0</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>대규모 트래픽 시 초과분</t>
+          <t>⚠ 카카오톡 채널 운영 시만 — 자체 푸시/이메일이면 0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>모니터링 (Sentry 무료 / 자체)</t>
+          <t>Firebase Auth (10K MAU 무료)</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
@@ -3479,14 +3490,14 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>자체 호스팅 시 0</t>
+          <t>매장 1K(MAU 50K)에서 일부 유료</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>번역 API (P8b)</t>
+          <t>Google Maps (월 $200 무료)</t>
         </is>
       </c>
       <c r="B19" s="19" t="n">
@@ -3496,88 +3507,136 @@
         <v>0</v>
       </c>
       <c r="D19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="E19" s="19" t="n">
-        <v>100000</v>
-      </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>DeepL — 채팅 자동 번역</t>
+          <t>대규모 트래픽 시 초과분</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
+          <t>모니터링 (Sentry 무료 / 자체)</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>자체 호스팅 시 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>번역 API (P8b)</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>DeepL — 채팅 자동 번역</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
           <t>자동화 (Mac mini 자체)</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="B22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>메모리 — Python 스크립트</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>월 운영비 합계</t>
         </is>
       </c>
-      <c r="B21" s="21">
-        <f>SUM(B9:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="21">
-        <f>SUM(C9:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="21">
-        <f>SUM(D9:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>SUM(E9:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="B23" s="21">
+        <f>SUM(B11:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="21">
+        <f>SUM(C11:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="21">
+        <f>SUM(D11:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
+        <f>SUM(E11:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>월 손익 (매출 − 비용)</t>
         </is>
       </c>
-      <c r="B22" s="29">
-        <f>B8-B21</f>
-        <v/>
-      </c>
-      <c r="C22" s="29">
-        <f>C8-C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="29">
-        <f>D8-D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="29">
-        <f>E8-E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="13" t="inlineStr"/>
+      <c r="B24" s="31">
+        <f>B9-B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="31">
+        <f>C9-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="31">
+        <f>D9-D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="31">
+        <f>E9-E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3655,10 +3714,10 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>'월별 운영비 시나리오'!B21</f>
-        <v/>
-      </c>
-      <c r="C4" s="30" t="n">
+        <f>'월별 운영비 시나리오'!B23</f>
+        <v/>
+      </c>
+      <c r="C4" s="32" t="n">
         <v>10</v>
       </c>
       <c r="D4" s="6">
@@ -3673,15 +3732,15 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>매장 100 (Y1 목표)</t>
+          <t>매장 10,000 (Y1 목표)</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'월별 운영비 시나리오'!C21</f>
-        <v/>
-      </c>
-      <c r="C5" s="30" t="n">
-        <v>100</v>
+        <f>'월별 운영비 시나리오'!C23</f>
+        <v/>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>10000</v>
       </c>
       <c r="D5" s="6">
         <f>C5*'월별 운영비 시나리오'!$E$3</f>
@@ -3695,15 +3754,15 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>매장 500 (Y2~3)</t>
+          <t>매장 30,000 (Y2~3)</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>'월별 운영비 시나리오'!D21</f>
-        <v/>
-      </c>
-      <c r="C6" s="30" t="n">
-        <v>500</v>
+        <f>'월별 운영비 시나리오'!D23</f>
+        <v/>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>30000</v>
       </c>
       <c r="D6" s="6">
         <f>C6*'월별 운영비 시나리오'!$E$3</f>
@@ -3717,15 +3776,15 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>매장 1000 (Y3+)</t>
+          <t>매장 70,000 (Y3+)</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>'월별 운영비 시나리오'!E21</f>
-        <v/>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>1000</v>
+        <f>'월별 운영비 시나리오'!E23</f>
+        <v/>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>70000</v>
       </c>
       <c r="D7" s="6">
         <f>C7*'월별 운영비 시나리오'!$E$3</f>
@@ -3760,7 +3819,7 @@
           <t>매장 10 시나리오 — BEP</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="33">
         <f>B4/'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
@@ -3775,10 +3834,10 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>매장 100 시나리오 — BEP</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
+          <t>매장 10,000 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B11" s="33">
         <f>B5/'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
@@ -3789,10 +3848,10 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>매장 500 시나리오 — BEP</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
+          <t>매장 30,000 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B12" s="33">
         <f>B6/'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
@@ -3803,10 +3862,10 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>매장 1000 시나리오 — BEP</t>
-        </is>
-      </c>
-      <c r="B13" s="31">
+          <t>매장 70,000 시나리오 — BEP</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
         <f>B7/'월별 운영비 시나리오'!$E$3</f>
         <v/>
       </c>
@@ -3815,7 +3874,7 @@
       <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>⚠ 수익 구조 분석</t>
         </is>
@@ -3956,7 +4015,7 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>※ 6/2주 외부 신청 시작. Mac mini 7월 셋업 (자체 호스팅 + Cloudflare Tunnel). 8월 출시 후 매장 0→10. 알림톡/카카오톡 미사용 — 자체 푸시·이메일로 대체</t>
         </is>
@@ -4105,7 +4164,7 @@
       <c r="M5" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="36">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
@@ -4152,7 +4211,7 @@
       <c r="M6" s="19" t="n">
         <v>5000</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="36">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -4199,7 +4258,7 @@
       <c r="M7" s="19" t="n">
         <v>21000</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="36">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -4246,7 +4305,7 @@
       <c r="M8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="36">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -4293,7 +4352,7 @@
       <c r="M9" s="19" t="n">
         <v>5000</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="36">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -4340,7 +4399,7 @@
       <c r="M10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="36">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -4387,7 +4446,7 @@
       <c r="M11" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="36">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -4434,7 +4493,7 @@
       <c r="M12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="36">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -4481,7 +4540,7 @@
       <c r="M13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="36">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -4528,7 +4587,7 @@
       <c r="M14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="36">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -4593,60 +4652,60 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="28">
         <f>B15</f>
         <v/>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>B16+C15</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>C16+D15</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>D16+E15</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>E16+F15</f>
         <v/>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="28">
         <f>F16+G15</f>
         <v/>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="28">
         <f>G16+H15</f>
         <v/>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="28">
         <f>H16+I15</f>
         <v/>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="28">
         <f>I16+J15</f>
         <v/>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="28">
         <f>J16+K15</f>
         <v/>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="28">
         <f>K16+L15</f>
         <v/>
       </c>
-      <c r="M16" s="27">
+      <c r="M16" s="28">
         <f>L16+M15</f>
         <v/>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="28">
         <f>N15</f>
         <v/>
       </c>
@@ -4706,7 +4765,7 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>※ Q1 매장 ~30, Q2 ~100, Q3 ~300, Q4 ~500. Mac mini 자체 호스팅 + 자동화. 이메일 Q2부터 SendGrid Essentials. 알림톡 미사용 — 자체 푸시 + 이메일</t>
         </is>
@@ -4855,7 +4914,7 @@
       <c r="M5" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="36">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
@@ -4902,7 +4961,7 @@
       <c r="M6" s="19" t="n">
         <v>5000</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="36">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -4949,7 +5008,7 @@
       <c r="M7" s="19" t="n">
         <v>21000</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="36">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -4996,7 +5055,7 @@
       <c r="M8" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="36">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -5043,7 +5102,7 @@
       <c r="M9" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="36">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -5090,7 +5149,7 @@
       <c r="M10" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="36">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -5137,7 +5196,7 @@
       <c r="M11" s="19" t="n">
         <v>20000</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="36">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -5184,7 +5243,7 @@
       <c r="M12" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="36">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -5231,7 +5290,7 @@
       <c r="M13" s="19" t="n">
         <v>80000</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="36">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -5278,7 +5337,7 @@
       <c r="M14" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="36">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -5343,60 +5402,60 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="28">
         <f>B15</f>
         <v/>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>B16+C15</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>C16+D15</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>D16+E15</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>E16+F15</f>
         <v/>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="28">
         <f>F16+G15</f>
         <v/>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="28">
         <f>G16+H15</f>
         <v/>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="28">
         <f>H16+I15</f>
         <v/>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="28">
         <f>I16+J15</f>
         <v/>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="28">
         <f>J16+K15</f>
         <v/>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="28">
         <f>K16+L15</f>
         <v/>
       </c>
-      <c r="M16" s="27">
+      <c r="M16" s="28">
         <f>L16+M15</f>
         <v/>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="28">
         <f>N15</f>
         <v/>
       </c>
